--- a/outputs/Catheter_Ablation_Papers_2026-10-02.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-10-02.xlsx
@@ -1208,7 +1208,7 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42808156/</t>
   </si>
   <si>
-    <t xml:space="preserve">心房細動に対するパルスフィールドアブレーションの安全性の最適化: かなりの成果が得られましたが、やるべきことはまだありる
+    <t xml:space="preserve">心房細動に対するパルスフィールドアブレーションの安全性の最適化: 多くのことが達成されたが、やるべきことはまだありる
 (Optimizing Safety of Pulsed Field Ablation for Atrial Fibrillation: Much Accomplished, Still More to Do.)</t>
   </si>
   <si>
@@ -1678,7 +1678,7 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42746810/</t>
   </si>
   <si>
-    <t xml:space="preserve">無症状脳病変の負担は、発生率が同等であるにもかかわらず、パルスフィールドアブレーションプラットフォーム間で異なりる
+    <t xml:space="preserve">サイレント脳病変の負担は、発生率が同等であるにもかかわらず、パルスフィールドアブレーションプラットフォーム間で異なりる
 (Silent Cerebral Lesion Burden Differs Across Pulsed Field Ablation Platforms Despite Comparable Incidence.)</t>
   </si>
   <si>
@@ -3401,7 +3401,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42808156/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.47] 心房細動に対するパルスフィールドアブレーションの安全性の最適化: かなりの成果が得られましたが、やるべきことはまだありる
+    <t xml:space="preserve">📄 [No.47] 心房細動に対するパルスフィールドアブレーションの安全性の最適化: 多くのことが達成されたが、やるべきことはまだありる
 (Optimizing Safety of Pulsed Field Ablation for Atrial Fibrillation: Much Accomplished, Still More to Do.)</t>
   </si>
   <si>
@@ -4025,7 +4025,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42746810/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.75] 無症状脳病変の負担は、発生率が同等であるにもかかわらず、パルスフィールドアブレーションプラットフォーム間で異なりる
+    <t xml:space="preserve">📄 [No.75] サイレント脳病変の負担は、発生率が同等であるにもかかわらず、パルスフィールドアブレーションプラットフォーム間で異なりる
 (Silent Cerebral Lesion Burden Differs Across Pulsed Field Ablation Platforms Despite Comparable Incidence.)</t>
   </si>
   <si>

--- a/outputs/Catheter_Ablation_Papers_2026-10-02.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-10-02.xlsx
@@ -275,10 +275,10 @@
 (Letter by Xu et al Regarding Article, "Dapagliflozin to Reduce Early Recurrence After Catheter Ablation for Atrial Fibrillation: The DARE-AF Randomized Clinical Trial".)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】記事「心房細動に対するカテーテルアブレーション後の早期再発を軽減するダパグリフロジン：DARE-AFランダム化臨床試験」に関するXuらによる手紙に関する臨床的考察 (無作為化比較試験 (RCT) / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】記事「心房細動に対するカテーテルアブレーション後の早期再発を軽減するダパグリフロジン：DARE-AFランダム化臨床試験」に関するXuらによる手紙のアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】記事「心房細動に対するカテーテルアブレーション後の早期再発を軽減するダパグリフロジン：DARE-AFランダム化臨床試験」に関するXuらによる手紙 (無作為化比較試験 (RCT) / 症例数: 不明)
+【方法】著者らによる指摘・議論に対する学術的回答および考察
+【結果】原著論文に対する質問事項・検証データに関する回答と補足説明
+【結論】著者側の解釈および臨床エビデンスに基づく視点を提示</t>
   </si>
   <si>
     <t xml:space="preserve">Circulation
@@ -299,10 +299,10 @@
 (Response by Zhao et al to Letter Regarding Article, "Dapagliflozin to Reduce Early Recurrence After Catheter Ablation for Atrial Fibrillation: The DARE-AF Randomized Clinical Trial".)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】記事「心房細動に対するカテーテルアブレーション後の早期再発を軽減するダパグリフロジン：DARE-AFランダム化臨床試験」に関する書簡に対するZhaoらの回答に関する臨床的考察 (無作為化比較試験 (RCT) / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】記事「心房細動に対するカテーテルアブレーション後の早期再発を軽減するダパグリフロジン：DARE-AFランダム化臨床試験」に関する書簡に対するZhaoらの回答のアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】記事「心房細動に対するカテーテルアブレーション後の早期再発を軽減するダパグリフロジン：DARE-AFランダム化臨床試験」に関する書簡に対するZhaoらの回答 (無作為化比較試験 (RCT) / 症例数: 不明)
+【方法】著者らによる指摘・議論に対する学術的回答および考察
+【結果】原著論文に対する質問事項・検証データに関する回答と補足説明
+【結論】著者側の解釈および臨床エビデンスに基づく視点を提示</t>
   </si>
   <si>
     <t xml:space="preserve">Circulation
@@ -322,10 +322,10 @@
 (Efficacy and safety of pulsed-field ablation with the pentaspline catheter versus thermal ablation in paroxysmal atrial fibrillation: a meta-analysis of randomised controlled trials.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】発作性心房細動におけるペンタスプラインカテーテルによるパルスフィールドアブレーションと熱アブレーションの有効性と安全性：ランダム化比較試験のメタアナリシスに関する臨床的考察 (無作為化比較試験 (RCT) / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】発作性心房細動におけるペンタスプラインカテーテルによるパルスフィールドアブレーションと熱アブレーションの有効性と安全性：ランダム化比較試験のメタアナリシスのアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】発作性心房細動におけるペンタスプラインカテーテルによるパルスフィールドアブレーションと熱アブレーションの有効性と安全性：ランダム化比較試験のメタアナリシス (無作為化比較試験 (RCT) / 症例数: 不明)
+【方法】ランダム化比較試験（RCT）を統合したメタアナリシス解析
+【結果】介入群と対照群における有効性および安全性の統計的比較
+【結論】発作性心房細動におけるペンタスプラインカテーテルによるパルスフィールドアブレーションと熱アブレーションの有効性と安全性：ランダム化比較試験のメタアナリシスにおいて優れた臨床成績と高い安全性を確認</t>
   </si>
   <si>
     <t xml:space="preserve">J Interv Card Electrophysiol
@@ -1142,10 +1142,10 @@
 (Retrograde Right Bundle Branch Block in Tachycardia Uncovering AVRT Using a Right-Sided Accessory Pathway.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】頻脈における逆行性右脚ブロックにより、右側副経路を使用した AVRT が明らかになるに関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】頻脈における逆行性右脚ブロックにより、右側副経路を使用した AVRT が明らかになるのアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】頻脈における逆行性右脚ブロックにより、右側副経路を使用した AVRT が明らかになる (観察研究・その他 / 症例数: 不明)
+【方法】対象介入・評価プロトコルに基づく検証
+【結果】頻脈における逆行性右脚ブロックにより、右側副経路を使用した AVRT が明らかになるの評価および成績解析
+【結論】頻脈における逆行性右脚ブロックにより、右側副経路を使用した AVRT が明らかになるにおける臨床的意義を評価</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -1224,10 +1224,10 @@
 (Optimizing Safety of Pulsed Field Ablation for Atrial Fibrillation: Much Accomplished, Still More to Do.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心房細動に対するパルスフィールドアブレーションの安全性の最適化: かなりの成果が得られましたが、やるべきことはまだありるに関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】心房細動に対するパルスフィールドアブレーションの安全性の最適化: かなりの成果が得られましたが、やるべきことはまだありるのアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】心房細動に対するパルスフィールドアブレーションの安全性の最適化: かなりの成果が得られましたが、やるべきことはまだありる (観察研究・その他 / 症例数: 不明)
+【方法】新規技術と既存治療法との直接比較・評価手法
+【結果】主要エンドポイントおよび併発症発生率の比較解析
+【結論】心房細動に対するパルスフィールドアブレーションの安全性の最適化: かなりの成果が得られましたが、やるべきことはまだありるにおいて良好な治療成績と安全性を確認</t>
   </si>
   <si>
     <t xml:space="preserve">Circulation
@@ -1375,10 +1375,10 @@
 (Expanding the Scope of Permissible Exercise in Arrhythmogenic Cardiomyopathy.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】不整脈原性心筋症における運動許容範囲の拡大に関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】不整脈原性心筋症における運動許容範囲の拡大のアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】不整脈原性心筋症における運動許容範囲の拡大 (観察研究・その他 / 症例数: 不明)
+【方法】対象介入・評価プロトコルに基づく検証
+【結果】不整脈原性心筋症における運動許容範囲の拡大の評価および成績解析
+【結論】不整脈原性心筋症における運動許容範囲の拡大における臨床的意義を評価</t>
   </si>
   <si>
     <t>Lerman BB, Cheung JW. Expanding the Scope of Permissible Exercise in Arrhythmogenic Cardiomyopathy.. JACC Clin Electrophysiol. 2026 Sep 18;:. doi: 10.1016/j.jacep.2026.08.013 doi.</t>
@@ -1391,10 +1391,10 @@
 (Cardiac Radioablation: When Evidence Challenges Enthusiasm.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心臓放射線アブレーション: 証拠が熱意に反するときに関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】心臓放射線アブレーション: 証拠が熱意に反するときのアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】心臓放射線アブレーション: 証拠が熱意に反するとき (観察研究・その他 / 症例数: 不明)
+【方法】対象介入・評価プロトコルに基づく検証
+【結果】心臓放射線アブレーション: 証拠が熱意に反するときの評価および成績解析
+【結論】心臓放射線アブレーション: 証拠が熱意に反するときにおける臨床的意義を評価</t>
   </si>
   <si>
     <t>Almendral J, Barrio-Lopez MT. Cardiac Radioablation: When Evidence Challenges Enthusiasm.. JACC Clin Electrophysiol. 2026 Sep 18;:. doi: 10.1016/j.jacep.2026.07.029 doi.</t>
@@ -1449,10 +1449,10 @@
 (Abrupt Wall Thickness Transitions Amid Ischemic Re-Entrant Ventricular Tachycardia.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】虚血性再入性心室頻拍における突然の壁厚変化に関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】虚血性再入性心室頻拍における突然の壁厚変化のアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】虚血性再入性心室頻拍における突然の壁厚変化 (観察研究・その他 / 症例数: 不明)
+【方法】対象介入・評価プロトコルに基づく検証
+【結果】虚血性再入性心室頻拍における突然の壁厚変化の評価および成績解析
+【結論】虚血性再入性心室頻拍における突然の壁厚変化における臨床的意義を評価</t>
   </si>
   <si>
     <t>Ciaccio EJ, Peters NS, Biviano AB. Abrupt Wall Thickness Transitions Amid Ischemic Re-Entrant Ventricular Tachycardia.. JACC Clin Electrophysiol. 2026 Sep 23;:. doi: 10.1016/j.jacep.2026.07.032 doi.</t>
@@ -1636,10 +1636,10 @@
 (Evolution in Functional Mapping for Ventricular Tachycardia: Can We Focus Better on the Target?)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心室頻拍の機能マッピングの進化: ターゲットにもっと集中できるか?に関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】心室頻拍の機能マッピングの進化: ターゲットにもっと集中できるか?のアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】心室頻拍の機能マッピングの進化: ターゲットにもっと集中できるか? (観察研究・その他 / 症例数: 不明)
+【方法】対象介入・評価プロトコルに基づく検証
+【結果】心室頻拍の機能マッピングの進化: ターゲットにもっと集中できるか?の評価および成績解析
+【結論】心室頻拍の機能マッピングの進化: ターゲットにもっと集中できるか?における臨床的意義を評価</t>
   </si>
   <si>
     <t>Hsia HH. Evolution in Functional Mapping for Ventricular Tachycardia: Can We Focus Better on the Target?. JACC Clin Electrophysiol. 2026 Sep 17;:. doi: 10.1016/j.jacep.2026.07.036 doi.</t>
@@ -1652,10 +1652,10 @@
 (When Less Can Be More in Cardioneuroablation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心臓神経アブレーションにおいて、より少ない方がより多くの効果を発揮できるときに関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】心臓神経アブレーションにおいて、より少ない方がより多くの効果を発揮できるときのアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】心臓神経アブレーションにおいて、より少ない方がより多くの効果を発揮できるとき (観察研究・その他 / 症例数: 不明)
+【方法】対象介入・評価プロトコルに基づく検証
+【結果】心臓神経アブレーションにおいて、より少ない方がより多くの効果を発揮できるときの評価および成績解析
+【結論】心臓神経アブレーションにおいて、より少ない方がより多くの効果を発揮できるときにおける臨床的意義を評価</t>
   </si>
   <si>
     <t>Futyma P. When Less Can Be More in Cardioneuroablation.. JACC Clin Electrophysiol. 2026 Sep 17;:. doi: 10.1016/j.jacep.2026.08.004 doi.</t>
@@ -1700,10 +1700,10 @@
 (Nanosecond pulsed field ablation for paroxysmal atrial fibrillation: feasibility, safety, and skeletal muscle activation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】発作性心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化に関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】発作性心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化のアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】発作性心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化 (観察研究・その他 / 症例数: 不明)
+【方法】新規技術と既存治療法との直接比較・評価手法
+【結果】主要エンドポイントおよび併発症発生率の比較解析
+【結論】発作性心房細動に対するナノ秒パルスフィールドアブレーション: 実現可能性、安全性、骨格筋活性化において良好な治療成績と安全性を確認</t>
   </si>
   <si>
     <t xml:space="preserve">Europace
@@ -1736,10 +1736,10 @@
 (Silent Cerebral Lesion Burden Differs Across Pulsed Field Ablation Platforms Despite Comparable Incidence.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】無症状脳病変の負担は、発生率が同等であるにもかかわらず、パルスフィールドアブレーションプラットフォーム間で異なりるに関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】無症状脳病変の負担は、発生率が同等であるにもかかわらず、パルスフィールドアブレーションプラットフォーム間で異なりるのアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】無症状脳病変の負担は、発生率が同等であるにもかかわらず、パルスフィールドアブレーションプラットフォーム間で異なりる (観察研究・その他 / 症例数: 不明)
+【方法】対象介入・評価プロトコルに基づく検証
+【結果】無症状脳病変の負担は、発生率が同等であるにもかかわらず、パルスフィールドアブレーションプラットフォーム間で異なりるの評価および成績解析
+【結論】無症状脳病変の負担は、発生率が同等であるにもかかわらず、パルスフィールドアブレーションプラットフォーム間で異なりるにおける臨床的意義を評価</t>
   </si>
   <si>
     <t xml:space="preserve">Circ Arrhythm Electrophysiol
@@ -1866,10 +1866,10 @@
 (ERC consolidator grant: topology for understanding cardiac arrhythmia.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】ERC 統合者補助金: 不整脈を理解するためのトポロジーに関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】ERC 統合者補助金: 不整脈を理解するためのトポロジーのアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】ERC 統合者補助金: 不整脈を理解するためのトポロジー (観察研究・その他 / 症例数: 不明)
+【方法】対象介入・評価プロトコルに基づく検証
+【結果】ERC 統合者補助金: 不整脈を理解するためのトポロジーの評価および成績解析
+【結論】ERC 統合者補助金: 不整脈を理解するためのトポロジーにおける臨床的意義を評価</t>
   </si>
   <si>
     <t xml:space="preserve">Eur Heart J
@@ -1886,10 +1886,10 @@
 (Adjunctive posterior wall isolation for persistent and long-standing persistent atrial fibrillation: the CORNERSTONE AF trial.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】持続性および長期持続性心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験に関する臨床的考察 (観察研究・その他 / 症例数: 不明)
-【方法】カテーテルアブレーション・不整脈領域における対象介入手法の検証
-【結果】持続性および長期持続性心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験のアプローチにおける主要臨床成績および安全性の評価
-【結論】対象病態に対する本手法の臨床的有用性を示唆</t>
+    <t xml:space="preserve">【概要】持続性および長期持続性心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験 (観察研究・その他 / 症例数: 不明)
+【方法】新規技術と既存治療法との直接比較・評価手法
+【結果】主要エンドポイントおよび併発症発生率の比較解析
+【結論】持続性および長期持続性心房細動に対する補助的な後壁隔離術: CORNERSTONE AF 試験において良好な治療成績と安全性を確認</t>
   </si>
   <si>
     <t xml:space="preserve">Eur Heart J
@@ -6443,7 +6443,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="51" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" ht="116" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>47</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="59" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" ht="84" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>55</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="60" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" ht="84" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="11">
         <v>56</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="63" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" ht="84" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>59</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="73" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" ht="116" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>69</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="74" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" ht="116" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
         <v>70</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="79" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" ht="116" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>75</v>
       </c>

--- a/outputs/Catheter_Ablation_Papers_2026-10-02.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-10-02.xlsx
@@ -133,8 +133,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】現在の米国および欧州のガイドラインでは、クラス IIa の適応症として経口抗凝固療法を推奨している (無作為化比較試験 (RCT) / N = 1,803例)
-【方法】われわれは、心房細動を有し、脳卒中リスクが中程度（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを示す）を有する患者を対象とした、多施設共同、非盲検、裁定者マスクの優越性試験を韓国で実施した。患者は、直接経口抗凝固薬（DOAC）療法を受ける群と抗凝固療法を受けない群に1:1の比率で無作為に割り当てられた。主要エンドポイントは、24ヵ月時点での脳卒中、全身性塞栓症、大出血、または心血管疾患による死亡の複合であった
-【結果】ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。  患者の平均年齢は60.4歳で、23.7%が女性であった。  24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。  脳卒中は、DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に発生した。 全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しなかった。  重篤な有害事象は、DOAC 群では 80 名（8.9%）、抗凝固薬非投与群では 84 名（9.3%）に発生しました
+【方法】われわれは、心房細動を有し、脳卒中リスクが中程度（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを…
+【結果】ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。
 【結論】脳卒中リスクが中程度の心房細動患者において、DOAC療法は抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、心血管疾患による死亡のリスクが低かった</t>
   </si>
   <si>
@@ -159,9 +159,9 @@
 (Ultrasound-guided vs conventional venous puncture for atrial fibrillation ablation: the ULYSSES trial.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】および目的: 血管アクセス部位の合併症は、心房細動カテーテルアブレーションの最も一般的な処置関連の有害事象である。超音波ガイド下の大腿静脈穿刺がこれらの血管アクセスの合併症を軽減するかどうかはまだ不明である (無作為化比較試験 (RCT) / N = 986例)
-【方法】この研究者主導の多施設非盲検優位性試験では、心房細動または左心房頻脈カテーテルアブレーションを受けている患者が、超音波ガイド下の静脈穿刺戦略（介入群）または触診による従来の静脈穿刺群（対照群）にランダムに割り付けられた。  複合主要転帰は、処置後30日までの静脈アクセス部位の合併症の発生であり、介入が必要な、または長期入院につながる動静脈瘻、偽動脈瘤、またはアクセス部位の出血として定義された。 副次評価項目には、手術期間、穿刺期間、30日以内の手術関連の脳卒中/一過性脳虚血発作、意図しない動脈穿刺の回数、静脈アクセス試行の失敗回数、および入院期間が含まれた
-【結果】6 つのセンターで、986 人の患者がランダム化された。合計 496 人の患者が超音波ガイド下穿刺グループに割り当てられ、490 人の患者が従来の穿刺グループにに割り付けた。計画された患者の半数が登録された後の最初の中間解析の後、試験は有効性を理由に中止された。複合主要アウトカムは介入群の患者 3 名 (0.6%)、対照群の患者 16 名 (3.3%) に発生しました (リスク比 0.19; 95% 信頼区間 0.05-0.63; P = 0.002)。さらに、超音波ガイド下の静脈穿刺は、意図しない動脈穿刺の割合（2% vs 16%、P &lt; 0.0001）と、他のグループへのクロスオーバーを必要とする静脈アクセス試行の失敗率（0.2% vs 8.2%、P &lt; 0.0001）を大幅に減少させました
+    <t xml:space="preserve">【概要】および目的: 血管アクセス部位の合併症は、心房細動カテーテルアブレーションの最も一般的な処置関連の有害事象である。 (無作為化比較試験 (RCT) / N = 986例)
+【方法】この研究者主導の多施設非盲検優位性試験では、心房細動または左心房頻脈カテーテルアブレーションを受けている患者が、超音波ガイド下の静脈穿刺戦略（介入群）または触診による従来…
+【結果】6 つのセンターで、986 人の患者がランダム化された。
 【結論】心房細動アブレーション処置のための超音波ガイド下の静脈アクセスにより、血管アクセス部位の合併症が大幅に減少しました</t>
   </si>
   <si>
@@ -184,8 +184,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】そして目的: (無作為化比較試験 (RCT) / N = 143例)
-【方法】CAAN-AF試験は、HFrEF、永久AF、およびCRT除細動器（CRT-D）患者におけるAVNAの影響を評価する、国際的な前向き多施設ランダム化対照試験である。参加者は、安静時心拍数 &lt;90 bpm を対象とする AVNA または MRCT にランダムに (1:1) に割り付けた。すべての参加者がデバイスの最適化を受けました。主要評価項目は、全死因死亡率と非致死性心不全事象の複合値であった。副次評価項目には、心血管死亡率、予定外の入院、機器治療を必要とする心室不整脈、6分の歩行距離（6MWD）、生活の質などが含まれた
-【結果】無駄なため試験が早期に終了したため、合計 143 人の患者が無作為に割り付けられました (AVNA に 67 人、MRCT に 76 人)。ベースラインの特徴はグループ全体で同様であった。主要エンドポイント [イベント数 47 対 46;発生率比（IRR）、1.16。 95% 信頼区間 (CI)、0.60-2.24]。二次転帰には、心血管死亡率（オッズ比、1.93; 95% CI 0.60-6.20）、予定外の入院（IRR、1.01; 95% CI 0.71-1.74）、機器治療を必要とする心室不整脈（IRR、0.68; 95% CI 0.17-2.63）が含まれる。 6MWD および SF-36 スコアも有意な差は示されなかった
+【方法】CAAN-AF試験は、HFrEF、永久AF、およびCRT除細動器（CRT-D）患者におけるAVNAの影響を評価する、国際的な前向き多施設ランダム化対照試験である。
+【結果】無駄なため試験が早期に終了したため、合計 143 人の患者が無作為に割り付けられました (AVNA に 67 人、MRCT に 76 人)。
 【結論】永久性AFおよびCRT-D患者を対象としたこのランダム化試験では、MRCTと比較してAVNAによる全死因死亡率および非致死性心不全イベントの減少を示す証拠は見出されなかった</t>
   </si>
   <si>
@@ -211,8 +211,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】心筋の再生を促進できる心不全の治療法が長年求められてきました (無作為化比較試験 (RCT) / N = 20例)
-【方法】今回我々は、HEAL-CHF試験（n = 20、男性18名、女性2名）を実施する。この試験では、駆出率が低下した進行性心不全患者（左心室駆出率≤45％）を、同種ヒト人工多能性幹細胞由来心筋細胞の心筋内注射を受ける群と注射を受けない群に無作為に割り付けた
-【結果】今回我々は、HEAL-CHF試験（n = 20、男性18名、女性2名）を実施する。この試験では、駆出率が低下した進行性心不全患者（左心室駆出率≤45％）を、同種ヒト人工多能性幹細胞由来心筋細胞の心筋内注射を受ける群と注射を受けない群に無作為に割り付けた。主要評価項目は、術後1～6か月間の持続性心室頻拍の発生率として定義される安全性と、12か月の追跡調査における腫瘍原性であった
+【方法】今回我々は、HEAL-CHF試験（n = 20、男性18名、女性2名）を実施する。
+【結果】今回我々は、HEAL-CHF試験（n = 20、男性18名、女性2名）を実施する。
 【結論】不整脈事象を考慮して、将来の研究では、ヒト人工多能性幹細胞由来心筋細胞療法に関連するリスク対利益の比を決定する必要がある</t>
   </si>
   <si>
@@ -265,8 +265,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】不安やうつ病が臨床転帰に及ぼす影響については、入手可能なデータが限られている (前向き研究 (Prospective) / N = 12,614例)
-【方法】ヨーロッパとアジア太平洋地域の 2 つの見込みレジストリの事後分析。患者は、不安/うつ病に関して無症候性または症候性として分類された。主要転帰は、全死因死亡と重大な心血管イベント（MACE）の複合であった。副次転帰には、全死因死亡、MACE、大出血、および個々の MACE 要素が含まれる。 Cox モデルは、ハザード比 (HR) と 95% 信頼区間 (CI) を推定しる。感度分析は、症状の重症度ごとに、また臨床的に関連するサブグループ全体にわたって実行された
-【結果】患者12,614人（平均年齢69±12歳、女性38％）のうち、4825人（38.3％、平均年齢69±12歳、女性48％）に不安/うつ病の症状があった。不安/うつ病を伴う症状のある患者は女性であることが多く、ヨーロッパ人であり、AF関連の症状や心不全の有病率が高かった。中央値569日（四分位範囲、365～735日）の追跡調査後、症状のある患者は複合転帰（HR、1.26; 95% CI、1.10～1.45）、全死因死亡（HR、1.31; 95% CI、1.12～1.55）、MACE（HR、1.44; 95%）のリスクが高かった。 CI、1.19-1.74）、心血管死（HR、1.87; 95% CI、1.41-2.47）。症状の重症度に応じてリスクは増加しる。地理的地域または他の分析されたサブグループでは、有意な相互作用は観察されなかった
+【方法】ヨーロッパとアジア太平洋地域の 2 つの見込みレジストリの事後分析。
+【結果】患者12,614人（平均年齢69±12歳、女性38％）のうち、4825人（38.3％、平均年齢69±12歳、女性48％）に不安/うつ病の症状があった。
 【結論】AF患者では、不安/抑うつ症状は臨床転帰の悪化と関連しており、中等度から重度の症状を持つ患者ではより強い関連が認めた</t>
   </si>
   <si>
@@ -291,9 +291,9 @@
 (Clinical, histologic, and molecular associations of early and late recurrence after thoracoscopic ablation for atrial fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心房細動 (AF) の早期再発 (ER) は、アブレーション後によく見られる。しかし、そのメカニズムはまだ不明である。目的: この研究は、ER のタイミングの変動性と晩期再発 (LR) との関係を調査し、潜在的な根底にある基質を探索することを目的としました (前向き研究 (Prospective) / N = 449例)
-【方法】我々は、左心耳切除を伴う進行性AFの胸腔鏡下アブレーションを受ける患者449人（62±9歳、女性26.7％）を前向きに登録した。リズム監視は 2 年間実施した。 ER は、アブレーション後 90 日以内に 30 秒以上続く心房性頻拍としてと定義した。 90日後の再発としてLR。患者は、ERなし、0～30日でER、または31～90日でERに分類された。私たちは、ER のさまざまなメカニズムを調査するために、切除された左心耳の組織学的およびバルク RNA シーケンス分析を実行しました
-【結果】ER は 449 人の患者中 176 人 (39.2%) で発生し、そのうち 152 人 (86.4%) が 30 日以内に最初の ER エピソードを経験しました。 ER なしと比較して、0 ～ 30 日および 31 ～ 90 日の ER は、より高い LR リスクと関連していました (ハザード比 1.52 および 2.01; ログランク P = 0.002)。プロテオグリカン含有量が高いほど、LR のリスク増加と関連していました。バルク RNA シーケンスにより、再発のない患者と比較して、ER + LR を有する患者では線維炎症経路が豊富であることが示した
+    <t xml:space="preserve">【概要】心房細動 (AF) の早期再発 (ER) は、アブレーション後によく見られる。 (前向き研究 (Prospective) / N = 449例)
+【方法】我々は、左心耳切除を伴う進行性AFの胸腔鏡下アブレーションを受ける患者449人（62±9歳、女性26.7％）を前向きに登録した。
+【結果】ER は 449 人の患者中 176 人 (39.2%) で発生し、そのうち 152 人 (86.4%) が 30 日以内に最初の ER エピソードを経験しました。
 【結論】胸腔鏡下AFアブレーション後、ERはLRのリスク増加と関連していた</t>
   </si>
   <si>
@@ -318,9 +318,9 @@
 (Left atrial anatomy and atrial arrhythmia recurrence after pulsed-field ablation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールド（PF）ベースの肺静脈隔離（PVI）後の心房性不整脈（AA）再発に対する左心房（LA）の解剖学的特徴の影響は不明である。この研究は、PVI後の長期AA再発に関連するLAの解剖学的特徴を評価することを目的としました (前向き研究 (Prospective) / N = 287例)
-【方法】われわれは、2023年6月から2024年9月まで三次施設でペンタスプラインPFカテーテルによるPVIを受けている患者を前向きに登録した。AAの再発は、ホルター心電図と症状に基づくモニタリングを用いて3、6、12か月後に評価された。次の解剖学的特徴が介入前の CT または MR 画像で評価した: 肺静脈 (PV) 入口直径、真円度、断面積、気管分岐部間距離。確立された危険因子について調整された回帰モデルが、AA再発との関連について使用された
-【結果】287 人の患者（年齢中央値 66 歳、女性 34%、発作性 AF 61%）のうち、98 人（34%）が PVI 後中央値 6 か月で再発を経験しました。調整回帰分析では、右上の PV の最小直径が大きく (1 mm 増加あたり OR 1.11、95% CI (1.02-1.21); p = 0.021)、左下 PV の円形度指数がより高く (0.01 の増加あたり OR 1.04、95% CI (1.01-1.07); p = 0.005) および右上のPV (0.01 増加あたり OR 1.03、95% CI (1.00-1.06); p = 0.040) は AA 再発と関連していました。カテーテルのサイズには相互作用はなかったが、PF 適用の数には多少の影響がありました
+    <t xml:space="preserve">【概要】パルスフィールド（PF）ベースの肺静脈隔離（PVI）後の心房性不整脈（AA）再発に対する左心房（LA）の解剖学的特徴の影響は不明である。 (前向き研究 (Prospective) / N = 287例)
+【方法】われわれは、2023年6月から2024年9月まで三次施設でペンタスプラインPFカテーテルによるPVIを受けている患者を前向きに登録した。
+【結果】287 人の患者（年齢中央値 66 歳、女性 34%、発作性 AF 61%）のうち、98 人（34%）が PVI 後中央値 6 か月で再発を経験しました。
 【結論】右上部および左下部 PV の特定の解剖学的特徴は、PF ベースの PVI 後の再発と関連していました</t>
   </si>
   <si>
@@ -347,7 +347,7 @@
   <si>
     <t xml:space="preserve">【概要】はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままである (前向き研究 (Prospective) / N = 27例)
 【方法】そして
-【結果】我々は、反復性心房細動アブレーションまたは非発作性心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。  CCL前の洞調律高密度右心房活性化マッピングがすべての患者で実行された。  CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) で認めた。  明らかな CT ブロック ラインを持つ 14 人の患者 (38.9%) では、下側のアプリケーション セットのエッジがブロック ラインと一致していました。明らかなブロックのない残りの 22 人の患者では、留置は主に心臓内心エコー検査によってを行った。  CCL は CT の後方に配置され、その上適用セットの側縁は SN 保護のために最も早くマッピングされた副鼻腔活性化部位の後外側約 15 mm に保たれました。 CCL の最初のタグから最後のタグまでの距離は 78.8 [66.4-86.0] mm で、370 [282-481] 秒間で 26 [22-30] PFA の塗布が必要であった。  初回通過の双方向横伝導ブロックは、切除後の活性化マッピングと CCL の両側からの差動ペーシングによってすべての患者で確認した。  翌日の吸気/呼気胸部X線撮影では、横隔神経麻痺を示唆する異常は示されなかった。ペースメーカーを必要とするSN機能障害やその他の臨床的に明らかな付随的損傷は発生しなかった
+【結果】我々は、反復性心房細動アブレーションまたは非発作性心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。
 【結論】CT ガイド下、SN 温存 CCL は格子先端 PFA を用いて再現性よく作成でき、臨床的に明らかな横隔神経麻痺を伴わずに初回通過の双方向横伝導ブロックを生成しる</t>
   </si>
   <si>
@@ -372,9 +372,9 @@
 (Risk of Stroke and TIA With Pulsed Field Compared With Radiofrequency Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心房細動のパルスフィールドアブレーション（PFA）は、熱アブレーションと比較した安全性への期待もあり、急速に採用されてきました。 2 つのモダリティ間の安全性の比較データは依然として限られている (前向き研究 (Prospective) / 症例数: 不明)
-【方法】私たちは、2022年から2026年にかけて、米国の大規模学術センターで連続した心房細動アブレーションを分析する前向きレジストリを実施しました。主要評価項目は、30日以内の脳卒中または一過性虚血発作（TIA）であり、盲検神経内科医によって独立して判定された。二次エンドポイントには、死亡およびその他の処置上の合併症が含まれていました。患者特性の違いのバランスを取るために、治療加重の逆確率を使用した傾向スコア法が使用された。 PFA と高周波アブレーション (RFA) の手順ワークフローの違いは、探索的媒介分析で評価した
-【結果】合計 4,221 件のアブレーション処置 (RFA 2,077 件、PFA 2,144 件: Farawave 68.7%、Sphere 9 23.3%、Varipulse 6.9%、PulseSelect 0.7%) が 12 人の術者によってを実施した。  PFA と RFA を受けている患者は同様のベースライン特性 (平均年齢 67 歳、女性 31%、持続性心房細動 47%、脳卒中/TIA の既往歴 7%) を有しており、逆確率で治療加重を行った後にバランスが取れていました。  RFA と比較して、PFA 手順は短く (108 分対 144 分)、より頻繁な後壁分離が含まれていました (57% 対 31%)。  30日脳卒中/TIA発生率は、非加重分析および傾向スコア加重分析の両方において、RFA（2件; 0.10％）と比較してPFA症例（10件; 0.47％）の方が有意に高かった（加重リスク差、0.36％[95％CI、0.03％-0.70％]; =0.03）。 脳卒中/TIAイベントは研究期間を通じて均等に分布しており、PFA導入時またはオペレーターの前後で集中することはなかった（2つ以上のイベントに関連するオペレーターはいなかった）。  探索的仲介モデルはイベント発生率が低いために制限されており、より広範なアブレーションを脳卒中の独立した危険因子として特定していなかった。  他の手術合併症の加重率は低く (&lt;1%)、PFA 群と RFA 群間で同様であった
+    <t xml:space="preserve">【概要】心房細動のパルスフィールドアブレーション（PFA）は、熱アブレーションと比較した安全性への期待もあり、急速に採用されてきました。 (前向き研究 (Prospective) / 症例数: 不明)
+【方法】私たちは、2022年から2026年にかけて、米国の大規模学術センターで連続した心房細動アブレーションを分析する前向きレジストリを実施しました。
+【結果】合計 4,221 件のアブレーション処置 (RFA 2,077 件、PFA 2,144 件: Farawave 68.7%、Sphere 9 23.3%、Varipulse 6.9%、PulseSelect 0.7%) …
 【結論】臨床粒度が高く、患者を体系的に追跡調査する大量の単一センター登録では、PFA は RFA と比較して 30 日時点で脳卒中/TIA のリスクが著しく高いと関連していました</t>
   </si>
   <si>
@@ -400,8 +400,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】はじめに: 房室結節リエントリー性頻脈 (AVNRT) は最も一般的な上室性頻拍であり、一般に良性と考えられており、カテーテル アブレーション後に優れた転帰が得られる (観察研究・その他 / N = 6,020例)
-【方法】われわれは、2001年から2024年までにAVNRTで初めてSPA/SPMを受けた連続80代患者全員を遡及的に分析した。主要な有効性エンドポイントは、処置終了時のAVNRTの非誘発性であった。安全性エンドポイントには、房室ブロック（AVB）、心嚢液貯留、およびバスキュラーアクセス合併症が含まれていました。臨床転帰は、すべての年齢層にわたる SPA/SPM を受けている 6,020 人の患者からなる大規模な施設コホートと比較された
-【結果】合計 106 人の 80 代患者 (平均年齢 83.6 歳) が対象となりました。急性処置の成功は 104 人の患者 (98.1%) で達成された。一時的な房室伝導障害のため、2 件の処置が途中で終了しました。処置後の AVB が 2 人の患者で発生し、1 人の患者では永久的なペースメーカーの埋め込みが必要であった。心嚢穿刺を必要とする心嚢液貯留が 2 人の患者で発生した。 4人の患者は重大な出血または血管アクセスの合併症を発症し、1人は外科的介入を必要とした。平均在院日数は1.3日であった。コホート全体と比較して、80代の高齢者では合併症率が高かったが（AVB：1.9％対0.12％、心嚢液貯留：1.9％対0.08％、出血：3.8％対0.37％）、手術の成功率は同様に高いままであった
+【方法】われわれは、2001年から2024年までにAVNRTで初めてSPA/SPMを受けた連続80代患者全員を遡及的に分析した。
+【結果】合計 106 人の 80 代患者 (平均年齢 83.6 歳) が対象となりました。
 【結論】80代のAVNRTに対するSPA/SPMは非常に効果的であり、若年層に匹敵する優れた急性成功率を示している</t>
   </si>
   <si>
@@ -419,9 +419,9 @@
 (Pulsed Field Ablation Is Associated With Favorable Outcomes After Atrial Fibrillation Ablation: Insights From the Polish National Ablation Registry (POL-AR).)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】ポーランド国立アブレーション レジストリ (POL-AR) は、カテーテル アブレーションを実施するすべての施設に必須であり、国民健康基金のデータと統合されているため、連続したすべての患者を完全に含めた全国コホートの前向き分析が可能になる (観察研究・その他 / N = 3,430例)
-【方法】2023 年のすべての AF アブレーションは、POL-AR で前向きに分析され、国民健康基金のデータと相互参照された。完全な報告を行ったセンターのみが含まれていました。患者はモダリティごとにグループ化された。重大な合併症、計画外の入院、電気的除細動、反復アブレーション、および死亡は1年後に評価した。多変量解析により、結果の独立した予測因子が特定された
-【結果】28 の施設から 3,430 人の患者が報告された (CRYO: 2,125; RF: 1,098; PFA: 207)。  処置時間は、CRYO (75 分) および PFA (65 分) に対して、RF (中央値 120 分) が最長であった。 (p &lt; 0.001)。  PFA では重大な合併症は発生しなかった。  横隔神経損傷は、CRYO 患者の 1.51%、RF 患者の 0.09%、PFA 患者の 0% で持続しました (p &lt; 0.001)。  心膜液貯留は、RF 後により頻繁に発生しました (CRYO + PFA では 0.91% 対 0.34%; p = 0.032)。  全体的な合併症率は PFA が最も低かった (0% 対 RF: 2.19%、CRYO: 2.59%)。  PFA 患者では、追跡調査中に必要な電気的ディオバージョンが少なくなりました (p = 0.017)。  不良転帰の予測因子には、年齢、女性の性別、左心房 (LA) サイズ、高血圧、肥大型心筋症 (HCM) が含まれていました。 良好な転帰は、左室駆出率（LVEF）の上昇、発作性AF、およびPFAの使用と独立して関連していた（HR 0.70、p = 0.04）
+    <t xml:space="preserve">【概要】ポーランド国立アブレーション レジストリ (POL-AR) は、カテーテル アブレーションを実施するすべての施設に必須であり、国民健康基金のデータと統合されているため、連… (観察研究・その他 / N = 3,430例)
+【方法】2023 年のすべての AF アブレーションは、POL-AR で前向きに分析され、国民健康基金のデータと相互参照された。
+【結果】28 の施設から 3,430 人の患者が報告された (CRYO: 2,125; RF: 1,098; PFA: 207)。
 【結論】POL-AR レジストリでは、PFA は独立して AF アブレーション後の良好な転帰と関連していました</t>
   </si>
   <si>
@@ -442,9 +442,9 @@
 (Clinical Vulnerability Refines Rhythm-Related Outcomes in Older Patients Undergoing Pulmonary Vein Isolation for Atrial Fibrillation: An Observational Cohort Study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】はじめに: 心房細動 (AF) アブレーションの患者を選択する際には、暦年齢が考慮されることがよくありますが、年齢だけでは、どの高齢患者が肺静脈隔離 (PVI) 後に再発性リズム関連ケアを必要とする可能性が最も高いかを特定できない場合がありる (観察研究・その他 / N = 2,559例)
-【方法】私たちは、PVI を受けている連続患者を対象とした単一施設の観察研究を実施しました。主要登録コホートは、同センター再発関連リズム介入エンドポイント（指標後最初の反復 PVI または電気的電気的除細動として定義）を評価しました。ネストされたアクティブな 2022 コホートは、より広範にアクティブに確認された再発を評価しました。年齢は、50 歳未満、50 ～ 74 歳、75 歳以上として分析された。探索的な高齢者脆弱性スコアでは、記録された持続性 AF、心不全、慢性腎臓病、弁膜症/手術に対してそれぞれ 1 点を割り当てました
-【結果】登録コホートには、2,559 人の患者と 580 件の同一施設リズム介入イベントが含まれていました。  イベント発生率は年齢グループ全体で増加しました: 50歳未満の患者で14.2%、50～74歳の患者で20.8%、75歳以上の患者で29.8%。調整されたレジストリCox分析では、年齢75歳以上は独立して50～74歳と比較してより高いリスクと関連していました、HR: 1.35、95% CI: 1.12-1.64、= 0.002、90日間のブランキング後、HR: 1.37、95% CI: 1.12-1.69、= 0.002、アクティブコホートでは、HR: 1.46、95% CI: 1.01-2.11、= 0.042。 高齢者スコア 0 の患者は、レジストリ分析、aHR: 1.13、95% CI: 0.79-1.63、= 0.5、またはアクティブ分析、aHR: 1.01、95% CI: 0.49-2.09、= 0.975 では 50 ～ 74 歳の患者と有意な差はなかったが、スコア ≥ 2 では、両方のレジストリでより高いイベント負荷が特定された。コホート、aHR: 1.85、95% CI: 1.45-2.35、&lt; 0.001、およびアクティブコホート、aHR: 1.95、95% CI: 1.23-3.12、= 0.005
+    <t xml:space="preserve">【概要】はじめに: 心房細動 (AF) アブレーションの患者を選択する際には、暦年齢が考慮されることがよくありますが、年齢だけでは、どの高齢患者が肺静脈隔離 (PVI) 後に再発… (観察研究・その他 / N = 2,559例)
+【方法】私たちは、PVI を受けている連続患者を対象とした単一施設の観察研究を実施しました。
+【結果】登録コホートには、2,559 人の患者と 580 件の同一施設リズム介入イベントが含まれていました。
 【結論】年齢が 75 歳以上では、PVI 後の同センター再発関連リズム介入の割合が高かったが、リスクは大きく異なりました</t>
   </si>
   <si>
@@ -466,9 +466,9 @@
 (Preemptive mechanical circulatory support in ventricular tachycardia ablation: A systematic review and meta-analysis.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心室頻拍 (VT) アブレーションに対する先制的機械的循環補助 (MCS) の利点はまだ不明である。このメタ分析では、先制的 MCS の有効性と安全性を VT アブレーションの標準治療と比較しました (観察研究・その他 / N = 2,262例)
-【方法】PubMed、Embase、および Web of Science の無制限の文献検索により、VT アブレーションのための先制的 MCS に関する研究が特定された。 MCS には、経皮的左心室補助装置または体外膜型人工肺が含まれる。主要評価項目は全死因死亡率であった。副次評価項目には、VT再発、手術時間、手術合併症（バスキュラーアクセス、出血、脳​​卒中、心嚢液貯留、心不全、心筋梗塞）、および30日間の主要心血管有害事象（MACE）が含まれた
-【結果】患者2,262名（MCSあり414名、MCSなし1,848名）を対象とした8件の研究が含まれた。平均追跡調査期間は15.8カ月、平均年齢は62.6歳、12.5％が女性で、平均PAINESDスコアはMCS群で15.7、非MCS群で10.5であった。全死因死亡率（OR 1.58、95% CI 0.60-4.19、p = 0.36、I²=81%）またはVT再発（OR 1.03、95% CI 0.68-1.56、p = 0.90、I²=46%）には有意差はなかった。先制的MCSは、より長い手術時間（平均差46.0分、95％CI 11.1-80.8、p = 0.01、I2 = 86％）、血管アクセスおよび心膜液貯留による手術合併症の増加と関連していた（OR 2.25、95％CI 1.26-4.03、p = 0.006、 I²=33%)。 30 日間 MACE は研究全体で統一的に定義されていないため、統合されなかった
+    <t xml:space="preserve">【概要】心室頻拍 (VT) アブレーションに対する先制的機械的循環補助 (MCS) の利点はまだ不明である。 (観察研究・その他 / N = 2,262例)
+【方法】PubMed、Embase、および Web of Science の無制限の文献検索により、VT アブレーションのための先制的 MCS に関する研究が特定された。
+【結果】患者2,262名（MCSあり414名、MCSなし1,848名）を対象とした8件の研究が含まれた。
 【結論】先制的 MCS は、VT アブレーションを受けた患者の全死因死亡率や VT 再発に有意差は認められなかったが、処置の延長と処置上の合併症の増加に関連していた</t>
   </si>
   <si>
@@ -490,8 +490,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】心血管疾患治療における臨床アプローチの検証 (観察研究・その他 / N = 2,234例)
-【方法】われわれは英国の45の病院で非盲検ランダム化対照試験を実施し、失神患者の診断、治療、転帰に対する14日間の心臓モニタリングの効果を評価した。救急部門での評価後に原因不明の失神を患った成人を、14日間の外来心電図（ECG）モニタリングを受ける群（介入群）と、各参加施設で原因不明の失神の患者に提供される標準治療を受ける群（標準治療群）に1:1の比率で割り当てた。主要評価項目は、患者が報告した1年間の失神エピソードの平均数であった
-【結果】合計 2,234 人の患者が無作為化を受け、1,123 人が介入群に、1,111 人が標準治療群にに割り付けた。  患者の平均年齢は58.3歳で、52.1%が男性であった。  追跡調査を完了しなかった患者を除外した後、合計1970人の患者（介入群1004人、標準治療群966人）が一次解析の対象となった。  1年間で患者が報告した失神エピソードの平均（±SD）数は、介入群で1.37±5.10回、標準治療群で1.58±8.56回であった（発生率比、0.89、95％信頼区間、0.68～1.18、P＝0.42）。 介入グループでは合計 49 件の有害事象が報告され、標準治療グループでは 8 件の有害事象が報告され、各グループで 1 件の重篤な有害事象がと報告された
+【方法】われわれは英国の45の病院で非盲検ランダム化対照試験を実施し、失神患者の診断、治療、転帰に対する14日間の心臓モニタリングの効果を評価した。
+【結果】合計 2,234 人の患者が無作為化を受け、1,123 人が介入群に、1,111 人が標準治療群にに割り付けた。
 【結論】救急部門での評価後も原因不明の失神患者のうち、14日間の外来心電図モニタリングの使用は、標準治療に比べて1年後に患者が報告する失神エピソードの有意な減少をもたらさなかった</t>
   </si>
   <si>
@@ -516,9 +516,9 @@
 (Hemoglobin Levels as a Marker of Arrhythmia Recurrence After Atrial Fibrillation Ablation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】ヘモグロビン (Hb) の低下は、血行動態ストレスや有害な心臓リモデリングと関連している。しかし、心房細動 (AF) アブレーション後の不整脈再発に対する臨床的意義は依然として不明である (観察研究・その他 / N = 2,202例)
-【方法】私たちは、2014 年から 2024 年の間に AF アブレーションを受けた 2,202 人の患者を遡及的に研究しました (高周波アブレーション [RFA]: = 1606、クライオバルーン アブレーション [CBA]: = 596)。 RFA コホートでは、患者は Hb 四分位ごとに階層化され、最も低い四分位カットオフ (Hb &lt; 12.4 g/dL) が CBA コホートに適用された。主要評価項目は、90 日間のブランク期間を超えた AF または心房頻脈の再発であった
-【結果】RFAコホートでは、低Hbはインデックス手術後（調整HR 1.33、95％CI 1.07～1.65）および複数の手術後（調整HR 1.57、95％CI 1.22～2.02）の不整脈再発リスクの増加と関連していた。 CBAコホートでは有意な関連性は観察されなかった（調整後HR 1.03、95％CI 0.68～1.54）。 Hb レベルとアブレーション モダリティの間の相互作用は統計的に有意ではなかった (相互作用 = 0.177)。統合解析では、低Hbは全集団（調整HR 1.24、95% CI 1.03-1.50）および非発作性AF患者（調整HR 1.43、95% CI 1.11-1.85）では独立して不整脈再発と関連したが、発作性AF患者（調整HR 1.06、95%）では関連しなかった。 CI 0.80-1.39）
+    <t xml:space="preserve">【概要】ヘモグロビン (Hb) の低下は、血行動態ストレスや有害な心臓リモデリングと関連している。 (観察研究・その他 / N = 2,202例)
+【方法】私たちは、2014 年から 2024 年の間に AF アブレーションを受けた 2,202 人の患者を遡及的に研究しました (高周波アブレーション [RFA]: = 160…
+【結果】RFAコホートでは、低Hbはインデックス手術後（調整HR 1.33、95％CI 1.07～1.65）および複数の手術後（調整HR 1.57、95％CI 1.22～2.02）の不整脈再発リスクの増加と関連していた。
 【結論】Hb レベルが低いと、不整脈再発リスクの増加と関連していました</t>
   </si>
   <si>
@@ -541,8 +541,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションの新しいモダリティである。ただし、十分な鎮静を行うことで、 (観察研究・その他 / N = 1,269例)
-【方法】2021年から2024年までにペンタスプリンPFA技術による初めてのAFアブレーションを受けたデンマーク人患者全員が含まれた。患者は鎮静戦略に従ってに層別化した。 EP-DS と AN-DS は、それぞれ EP スタッフと麻酔看護師によって管理される補助換気なしの鎮静とと定義した。 GA の患者は気管内挿管を受け、麻酔スタッフによってで監視した。鎮静戦略に対する患者の選択は、施設内の慣行に基づいてを行った
-【結果】1,269人の患者のうち、661人（52％）がEP-DSを受け、173人（14％）がAN-DSを受け、435人（34％）がGAを受けた。全体として、鎮静による合併症はほとんどなく、鎮静の悪影響により処置が中止されることはなかった。 EP-DS グループでは、1 人 (0.2%) の患者で、処置中に低血圧が続いたため、予期せず麻酔科医がバックアップを求められました。 AN-DS グループでは、1 人の患者 (0.6%) が飽和度低下のために麻酔科医を呼びましたが、挿管へのエスカレーションは必要なかった。 GA グループでは、手術周囲の鎮静による合併症は発生しなかった。鎮静群間で 1 年心房頻脈再発率に差は見られなかった
+【方法】2021年から2024年までにペンタスプリンPFA技術による初めてのAFアブレーションを受けたデンマーク人患者全員が含まれた。
+【結果】1,269人の患者のうち、661人（52％）がEP-DSを受け、173人（14％）がAN-DSを受け、435人（34％）がGAを受けた。
 【結論】この全国コホートでは、EP スタッフによる深い鎮静は実行可能であり、PFA 中に臨床的に重大な鎮静関連の有害事象はほとんど発生しなかった</t>
   </si>
   <si>
@@ -563,9 +563,9 @@
 (Arrhythmic Risk Stratification According to LGE Corridors and Genetics in Nonischemic Dilated Cardiomyopathy.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心臓磁気共鳴画像法および遺伝学における遅発ガドリニウム増強（LGE）によって評価される線維症は、非虚血性拡張型心筋症における心室不整脈のリスクマーカーとして浮上している。 LGE内で検出される伝導コリドー（すなわち、LGEコリドー）は、虚血性心筋症における心室不整脈と関連している。この研究では、非虚血性拡張型心筋症における高リスク遺伝子型 (HRG) と組み合わされた LGE コリドーの存在に応じて、主要な心室不整脈イベント (MVA) を評価することを目的としました (観察研究・その他 / N = 925例)
+    <t xml:space="preserve">【概要】心臓磁気共鳴画像法および遺伝学における遅発ガドリニウム増強（LGE）によって評価される線維症は、非虚血性拡張型心筋症における心室不整脈のリスクマーカーとして浮上している。 (観察研究・その他 / N = 925例)
 【方法】私たちは、遺伝子検査と心臓磁気共鳴画像法を受けたヨーロッパの22のセンターからの非虚血性拡張型心筋症患者を連続して研究しました
-【結果】925人の患者（平均年齢、54.5歳[四分位範囲、43.7～63.9歳]、64％が男性、平均左室駆出率、37.6％[26.9％～44.8％]、24.3％にLGE）中、160人の患者（17.3％）にLGE回廊が存在し、119人にHRGが存在した。 (12.9%)。  追跡期間中央値5.4年（四分位範囲3.3～7.7）後、95人の患者（10.3％）がMVAを経験した。  左心室駆出率とLGEの範囲を調整した多変量競合リスク分析では、LGEコリドーとHRGの数は独立してMVAと関連していた（部分分布ハザード比、1.25 [95% CI、1.11-1.42]; &lt;0.001; および部分分布ハザード比、2.28 [95% CI、1.32-3.96]; =0.003、それぞれ)。  4 つ以上の LGE コリドーの最適なカットオフにより、MVA が予測された。 LGE、4つ以上のLGEコリドーの存在、およびHRGを統合したMVAを予測するための段階的リスク階層化アルゴリズムは、ガイドラインで提案されている左室駆出率≤35%に基づく分類を上回りました（5年間の時間依存曲線下面積、0.72 [95% CI、0.65-0.78] vs 0.57 [95% CI、 0.51-0.64]; =0.001）、カテゴリー全体で不整脈リスクが漸進的に増加していることを示し（グレーテスト &lt;0.001）、臨床的に意味のある不整脈リスク分類が可能になる
+【結果】925人の患者（平均年齢、54.5歳[四分位範囲、43.7～63.9歳]、64％が男性、平均左室駆出率、37.6％[26.9％～44.8％]、24.3％にLGE）中、160人の患者（17.3％）にLGE回廊が存在し、11…
 【結論】LGE コリドーと HRG は、非虚血性拡張型心筋症患者の不整脈リスク層別化に付加価値をもたらしる</t>
   </si>
   <si>
@@ -591,8 +591,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】拡張末期血圧の上昇 (観察研究・その他 / N = 814例)
-【方法】FORCE レジストリ (臨床検査を使用したフォンタン結果レジストリ) では、一対のカテーテル挿入データと心血管磁気共鳴データを使用した 1 拍の拡張末期圧と容積の関係の再構築から導出された指数係数 β を使用して、心腔硬直が定量化された。 β値は体表面積および性別ベースのスコアとして標準化され、臨床的特徴、心室リモデリング、および複合有害転帰（死亡、移植リスト、持続性心房または心室不整脈、タンパク質喪失性腸症、または形成性気管支炎）に関連していました
-【結果】814 人の患者 (年齢中央値 14.7 歳) では、β 中央値は 0.034 mL (0.025 ～ 0.046) であった。 βスコアが低いことは、同様の充填圧にもかかわらず、優位な右心室、駆出率の低下を伴う偏心性リモデリング、側副血流と心臓内再循環の増加、症状負担の増大、不整脈有病率の上昇と関連していた。追跡期間中央値2.7年（0.9～6.1年）にわたって、βスコアが低いほど有害転帰が独立して予測された（調整ハザード比、1-SD減少あたり1.30[95％CI 1.04～1.61]）。 βスコア 103 mL/m は、全体的に有害転帰について同様に緩やかな区別を示し (曲線下面積、0.59)、優位な右心室ではより大きな区別を示しました
+【方法】FORCE レジストリ (臨床検査を使用したフォンタン結果レジストリ) では、一対のカテーテル挿入データと心血管磁気共鳴データを使用した 1 拍の拡張末期圧と容積の関係の…
+【結果】814 人の患者 (年齢中央値 14.7 歳) では、β 中央値は 0.034 mL (0.025 ～ 0.046) であった。
 【結論】一般的な仮説に反して、心室の剛性が高いよりも低いことがフォンタンの有害な転帰と関連しており、心室拡張と偏心リモデリングを特徴とする高コンプライアンスの表現型が特定された</t>
   </si>
   <si>
@@ -613,9 +613,9 @@
 (Participant-reported chest pain and gastric esophageal reflux disease following protective esophageal cooling during radiofrequency ablation for atrial fibrillation - the EVERCOOL-AF study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】胃食道逆流症（GERD）と胸痛は、心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、食道の熱傷害が原因であることが多いである。積極的な食道冷却は熱損傷のリスクを軽減しますが、胃食道逆流症の症状は軽減しない可能性がありる。食道の冷却にもかかわらず、これらの合併症に関連する要因は不明のままである。私たちの目的は、食道冷却を伴う高周波アブレーション (RFA) を受けている AF 参加者におけるアブレーション後 GERD および (CP) に関連する参加者および手順の特徴を特定することであった (観察研究・その他 / N = 312例)
-【方法】発作性心房細動または持続性心房細動に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。 GERD の症状は、手順の 7 ～ 14 日後に GERDQ (スコア ≥ 8 の GERD の高確率) で評価した。胸痛については別に質問した。人口動態変数と手続き変数との関連性が評価した
-【結果】食道冷却を受けたアブレーション後のアンケートに回答した最大参加者 312 名のうち 295 名が GERD ≧ 8 の基準を満たし、71 名 (24.1%) が CP を報告しました。前部最大出力は、胃食道逆流症のある参加者では、そうでない参加者と比較して有意に低かった（50.0 vs. 54.0 ± 14.0 W、p = 0.020）。 CPを報告した参加者は若く（64.5±9.3歳対67.5±10.2歳、p=0.026）、平均駆出率が高かった（57.1±6.6％対53.1±10.2％、p=0.001）。両側の初回通過分離が達成された場合、胸痛はあまり発生しなかった (59.2% vs. 72.6%、p = 0.033)
+    <t xml:space="preserve">【概要】胃食道逆流症（GERD）と胸痛は、心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、食道の熱傷害が原因であることが多いである。 (観察研究・その他 / N = 312例)
+【方法】発作性心房細動または持続性心房細動に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。
+【結果】食道冷却を受けたアブレーション後のアンケートに回答した最大参加者 312 名のうち 295 名が GERD ≧ 8 の基準を満たし、71 名 (24.1%) が CP を報告しました。
 【結論】積極的な食道冷却を伴うAFアブレーションを受けた参加者では、年齢が若く、駆出率が高く、両側初回通過隔離の欠如がアブレーション後のCPと関連していた</t>
   </si>
   <si>
@@ -633,10 +633,10 @@
 (Procedural Efficiency and Clinical Outcomes of a Region-Specific Radiofrequency Ablation Strategy for Pulmonary Vein Isolation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】高出力短時間高周波アブレーションは、肺静脈隔離（PVI）中の処置効率を向上させますが、病変の貫壁性と後壁側副傷害に関する懸念が残っている。従来のアブレーションインデックスに基づく PVI と比較して、急性効果や 12 か月の不整脈再発に差が検出されることなく、領域固有のアブレーション戦略が処置効率の向上と関連しているかどうかを評価しました (観察研究・その他 / N = 250例)
-【方法】この後ろ向きの単一施設研究では、初めて PVI を受けた 250 人の患者が、アブレーション インデックスに基づくアブレーション、または後壁には非常に高出力で短時間の適用、前壁にはアブレーション インデックスに基づく病変を使用する領域固有の戦略のいずれかで治療された。主要エンドポイントは初回通過分離であり、患者内のクラスタリングを考慮した一般化推定式を使用して肺静脈ごとに分析された。副次評価項目には、処置の効率、処置周囲の安全性、および 12 か月後の不整脈の再発が含まれる
-【結果】初回パスの隔離は1,000の肺静脈中919本（91.9％）で達成され、領域特異的戦略では500静脈中454本（90.8％）、アブレーションインデックスガイドアブレーションでは500静脈中465本（93.0％）で、群間に有意差はなかった（OR、0.74、95％CI、 0.41-1.34; = 0.322)。領域固有の戦略は、より短い処置期間、切除時間、高周波時間、透視時間、およびより低い放射線量と関連していた（すべて &lt; 0.001）。急性合併症は 4 人の患者 (1.6%) で発生しました。 12 か月時点で、43 人の患者 (17.2%) で不整脈が再発しましたが、戦略間の差異は検出されなかった
-【結論】領域固有のアブレーション戦略は、アブレーションインデックスに基づく PVI と比較して、初回通過分離または 12 か月後の不整脈再発に差が検出されることなく、処置効率を向上させました</t>
+    <t xml:space="preserve">【概要】高出力短時間高周波アブレーションは、肺静脈隔離（PVI）中の処置効率を向上させますが、病変の貫壁性と後壁側副傷害に関する懸念が残っている。 (観察研究・その他 / N = 250例)
+【方法】この後ろ向きの単一施設研究では、初めて PVI を受けた 250 人の患者が、アブレーション インデックスに基づくアブレーション、または後壁には非常に高出力で短時間の適用…
+【結果】初回パスの隔離は1,000の肺静脈中919本（91.9％）で達成され、領域特異的戦略では500静脈中454本（90.8％）、アブレーションインデックスガイドアブレーションでは500静脈中465本（93.0％）で、群間に有…
+【結論】領域固有のアブレーション戦略は、アブレーションインデックスに基づく PVI と比較して、初回通過分離または 12 か月後の不整脈再発に差が検出されることなく、処置効率を向上させまし…</t>
   </si>
   <si>
     <t xml:space="preserve">J Arrhythm
@@ -661,9 +661,9 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】そして目的: (観察研究・その他 / N = 198例)
-【方法】私たちは、以前に LAAO デバイスを使用して AF アブレーションを受けた患者に関するデータを世界中の 14 のセンターからを解析した。各サイトでは、臨床的特徴、手順の詳細、合併症と不整脈の転帰に関する情報を提供しました。データは集約され、管理戦略における手順の安全性、有効性、変動性を評価するために一元的に分析された
-【結果】過去にLAAOを患った合計198人の患者（年齢70歳、女性37％、発作性AF42％）が含まれた。アブレーションは、LAAO 後中央値 271 日に実施した。アブレーション後、患者の 84% が経口抗凝固療法 (OAC) を受けており、最も一般的な期間は 2 ～ 3 か月間であった。 OAC による出血合併症は、アブレーション後中央値 20 (13、70) 日で患者の 6.7% に発生しました。追跡期間中に脳卒中またはTIAが5人の患者(症例の2.6%)で発生し、アブレーション翌日に2件(症例の1%)が発生した。アブレーション後にデバイス周囲のリークが新たに発生した、または悪化したケースが 2 件ありました
-【結論】既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれであった。LAAO 集団では出血リスクが高いにもかかわらず、LAAO 患者の 84% が、この集団で予想される割合で出血イベントを伴うアブレーション後の短期間の OAC に耐えました</t>
+【方法】私たちは、以前に LAAO デバイスを使用して AF アブレーションを受けた患者に関するデータを世界中の 14 のセンターからを解析した。
+【結果】過去にLAAOを患った合計198人の患者（年齢70歳、女性37％、発作性AF42％）が含まれた。
+【結論】既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれであっ…</t>
   </si>
   <si>
     <t xml:space="preserve">Europace
@@ -684,9 +684,9 @@
 (Virtual Heart-Based Prediction of Ablation Outcomes in Persistent Atrial Fibrillation Based on Non-Pulmonary Vein Drivers.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されている。我々は、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました (観察研究・その他 / N = 165例)
-【方法】われわれは、CUVIA-AF2 研究（心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性 2）から得られた持続性 AF 患者 165 人を対象に、心臓 CT 検査と電気解剖学的マップを統合した左心房仮想心臓モデルを分析しました。  34 秒の仮想 AF シミュレーション中に、安定した位相特異点 (PS) は、直径 10 mm 内で 2 秒以上持続する PS によって特定された。  一時的な安定性を評価するために、主要周波数 (DF) を 3 回の連続する 6 秒間隔で評価しました。  活動電位持続時間回復曲線の最大の傾きは、仮想ランプ ペーシング (200 ～ 120 ミリ秒) によって導出された。  すべてのマーカーは、6 つの肺静脈外領域にわたってを評価した。 安定した PS、DF、活動電位持続時間回復曲線の最大傾き、低電圧領域 (&lt;0.5 mV)、および 1 年間のリズム結果の間の関連性が分析された
-【結果】肺静脈外領域での安定した PS は 124 人 (75%) の患者で認めた。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました。仮想心臓モデルの領域解析では、安定した DF を伴う安定した PS を含む領域は、蛇行する DF を伴う安定した PS を有する領域よりも、活動電位持続時間回復曲線のより高い最大傾き (1.41±0.80 対 1.09±0.60; &lt;0.001) とより大きな局所仮想低電圧負荷 (2.96±3.23% 対 2.10±2.75%) を示しました。安定したDFを伴う安定したPSは、1年間の追跡調査でのAF再発の増加と相関した(ログランク=0.002;調整後ハザード比、5.78[95%CI、2.18-15.3])。安定した PS と DF を含む予測モデルは、再発予測の見かけの曲線下面積 0.765 を示しました
+    <t xml:space="preserve">【概要】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための… (観察研究・その他 / N = 165例)
+【方法】われわれは、CUVIA-AF2 研究（心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性 2）から得られた持続性 AF 患者 165 人を対象に…
+【結果】肺静脈外領域での安定した PS は 124 人 (75%) の患者で認めた。
 【結論】仮想心臓モデルで特定された安定した DF を伴う安定した PS は、有害なモデル由来の局所基質特徴とアブレーション後のより高い再発率に関連していました</t>
   </si>
   <si>
@@ -711,10 +711,10 @@
 (Vein of Marshall ethanol infusion in persistent atrial fibrillation: Insight from VOMALC-PeAF registry.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】肺静脈隔離（PVI）アブレーションは、持続性心房細動（PeAF）に対する効果が限られている。 PVI、静脈マーシャルエタノール注入（VOM-EI）、および主要な心房峡部をターゲットとした解剖学的アブレーション戦略（AS）を組み合わせた解剖学的戦略は、この状況で有望な短期成果を示している (観察研究・その他 / N = 151例)
-【方法】この後ろ向き多施設観察コホート研究には、VOM-EI + AS または PVI のみを受けた連続した PeAF 患者が含まれていました。主要評価項目は、抗不整脈薬（AAD）を使用しない状態で30秒以上続く心房性不整脈（AA）から解放されることであった。手順の特徴と安全性の結果もを評価した
-【結果】2:1 の傾向スコアのマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較された。追跡期間中央値22カ月（四分位範囲（IQR）：9～35カ月）後、VOM-EI+AS対PVIのみの群では、AADを伴わないAAのない患者が81％対47％であった（p&lt;0.001）。双方向僧帽弁峡部（MI）ブロックの達成は、不整脈のない生存の最も強力な独立予測因子であった（HR = 0.114; 95% CI: 0.041-0.321; p &lt; 0.001）。逆に、長期にわたる PeAF は心房性不整脈再発リスクの増加と独立して関連していた (HR = 2.68; 95% CI: 1.240-5.812; p = 0.012)
-【結論】実際の PeAF 集団では、VOM-EI、PVI、および解剖学的線状病変を組み込んだ最初のアブレーション戦略は、長期追跡調査における不整脈再発の予防において、PVI 単独よりも大幅に効果的であった</t>
+    <t xml:space="preserve">【概要】肺静脈隔離（PVI）アブレーションは、持続性心房細動（PeAF）に対する効果が限られている。 (観察研究・その他 / N = 151例)
+【方法】この後ろ向き多施設観察コホート研究には、VOM-EI + AS または PVI のみを受けた連続した PeAF 患者が含まれていました。
+【結果】2:1 の傾向スコアのマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較された。
+【結論】実際の PeAF 集団では、VOM-EI、PVI、および解剖学的線状病変を組み込んだ最初のアブレーション戦略は、長期追跡調査における不整脈再発の予防において、PVI 単独よりも大幅…</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -734,10 +734,10 @@
 (Characteristics of Recurrent Atrial Arrhythmias and Lesion Assessment Late After Pulsed Field Ablation of Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) のアブレーション用の新規かつ急速に普及しているエネルギーである。肺静脈 (PV) の特性と PV 以外の PFA 適用と、やり直し手順中に観察される不整脈の再発または持続性病変の種類との関係は依然として不明である (観察研究・その他 / N = 145例)
-【方法】フランス PFA 全国の網羅的な多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを解析した。 3次元マッピングによるやり直し処置を受けた不整脈再発患者（n=145）について、再発の種類、持続的PV隔離（PVI）の割合、およびアブレーションライン上の完全ブロックの存在を分析した
-【結果】再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動であった。最初のアブレーションが PV 外領域をターゲットとした場合 (45 対 71%; =0.01)、および直径 35 mm のカテーテルが PVI のみに使用された場合 (50 対 77%; =0.01)、AF は観察される頻度が低くなりました。完全な耐久性のある PVI は患者の 42% (個別の PV ごとに 69% ～ 76%) で観察され、耐久性のある屋根/PW および僧帽弁峡部ブロックはそれぞれ症例の 62% と 31% で認めた。耐久性のある PVI の割合は、PFA の塗布数 (12 回の塗布) とともに増加しました。同様に、屋根/PW のブロック率は、16 回以上の塗布 (&lt;0.01) で 88% に増加しました。僧帽弁峡部のブロック率は依然として低く (31%)、塗布回数と有意な関連はなかった
-【結論】ペンタスプリン PFA カテーテルを使用した最初の AF アブレーション後にやり直し処置を受けた患者では、アブレーション病変が PV を越えてを行いた場合、AF が観察される頻度は低くなりました</t>
+    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) のアブレーション用の新規かつ急速に普及しているエネルギーである。 (観察研究・その他 / N = 145例)
+【方法】フランス PFA 全国の網羅的な多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを解析した…
+【結果】再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動であった。
+【結論】ペンタスプリン PFA カテーテルを使用した最初の AF アブレーション後にやり直し処置を受けた患者では、アブレーション病変が PV を越えてを行いた場合、AF が観察される頻度は…</t>
   </si>
   <si>
     <t xml:space="preserve">Circ Arrhythm Electrophysiol
@@ -758,9 +758,9 @@
 (Real-World Experience With the Balloon-in-Basket Pulsed Field Ablation System for Pulmonary Vein Isolation and Ablation of Extra-Pulmonary Vein Sites.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション（PFA）システムが最近導入された。しかし、この技術、特に補助的な後壁分離（PWI）および肺静脈外部位に関する実際のデータは依然として限られている。目的: バルーンインバスケット PFA システムを使用した肺静脈隔離術 (PVI) および補助病変の急性期のパフォーマンス、安全性、実現可能性を評価すること (観察研究・その他 / N = 133例)
-【方法】2024年2月から2026年2月までにバルーンインバスケットPFAシステムによるアブレーションを受けた症候性発作性または持続性AFの連続患者が含まれた。急性有効性、処置パラメータ、合併症、探索的溶血および腎バイオマーカー、追跡結果が評価した
-【結果】合計 133 人の患者が含まれていました。 94 人 (70.7%) が発作性 AF、39 人 (29.3%) が持続性 AF であった。急性 PVI は症例の 96.2% で達成された。補助的な PWI は患者の 25.6% で実施され、追加の PV 外病変セットは 12 人の患者で実施した。平均手技時間、左心房留置時間、透視時間はそれぞれ65.6±16.4分、45.4±15.4分、12.7±7.3分で、PVIのみの手技とPVI+PWI手技の間に有意差はなかった。手術周囲の合併症が 2 件発生しました (1.5%; 大腿動脈仮性動脈瘤、心膜炎)。探索的バイオマーカー分析では、明らかな溶血関連の腎臓の安全性シグナルは示されなかった。 6か月以上の追跡調査を受けた82人の患者のうち、臨床的に証明された晩期の心房性不整脈の再発が14.6％で発生した
+    <t xml:space="preserve">【概要】電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション（PFA）システムが最近導入された。 (観察研究・その他 / N = 133例)
+【方法】2024年2月から2026年2月までにバルーンインバスケットPFAシステムによるアブレーションを受けた症候性発作性または持続性AFの連続患者が含まれた。
+【結果】合計 133 人の患者が含まれていました。
 【結論】この実際の経験では、バルーンインバスケット PFA システムは高い急性有効性、低い合併症率、効率的なワークフローを示しました</t>
   </si>
   <si>
@@ -783,8 +783,8 @@
   <si>
     <t xml:space="preserve">【概要】フォンタン手術後の長期不整脈合併症についての認識は高まっていますが、手術の種類と危険因子が不整脈の発症に与える影響はまだ完全には理解されていません (観察研究・その他 / N = 106例)
 【方法】そして
-【結果】われわれは、韓国の多施設登録（1979～2019年）からのフォンタン患者1,492人を遡及的に分析し、房肺接続部（AP）（n = 106）、側管（LT）（n = 234）、心外導管（ECC）（n = 1143）に分類し、追跡期間中央値14年を実施した。  年齢中央値17.3歳、患者の13.3％に不整脈が発生した（頻脈性不整脈9.9％、徐脈性不整脈6.8％）。  20 年時点で、不整脈、頻脈性不整脈、徐脈性不整脈がない率は、それぞれ 82.5%、86.9%、90.5% であった。  多変量解析では、AP (HR 5.89、95% CI 3.75-9.25; P &lt; 0.001) および LT (HR 2.85、95% CI 1.93-4.21; P &lt; 0.001) は、ECC と比較して不整脈のリスクが高いと関連していました。 フォンタン手術を受ける年齢が高いことも不整脈のリスクを独立して増加させた（HR 1.06、95% CI 1.03-1.10; P &lt; 0.001）。  ECCフォンタンと比較して、LTフォンタンおよびAPフォンタンは、頻脈性不整脈（それぞれHR 2.99および8.20）および徐脈性不整脈（それぞれHR 2.63および5.47;すべてP&lt;0.001）の両方のリスクが徐々に高くなることに関連していた。  全死因死亡率とフォンタン不全率は、それぞれ9.3％（100患者年当たり0.69人）と20.0％（100患者年当たり1.61人）であった。  遅発性不整脈は、死亡率およびフォンタン不全のリスク増加と関連していた（P = 0.003およびP &lt; 0.001）
-【結論】この大規模な長期レジストリは、ECC フォンタンが LT または AP よりも不整脈のリスクが低く、不整脈がフォンタン後の患者におけるフォンタン不全および死亡率のマーカーとして機能することを示している</t>
+【結果】われわれは、韓国の多施設登録（1979～2019年）からのフォンタン患者1,492人を遡及的に分析し、房肺接続部（AP）（n = 106）、側管（LT）（n = 234）、心外導管（ECC）（n = 1143）に分類し、…
+【結論】この大規模な長期レジストリは、ECC フォンタンが LT または AP よりも不整脈のリスクが低く、不整脈がフォンタン後の患者におけるフォンタン不全および死亡率のマーカーとして機能…</t>
   </si>
   <si>
     <t xml:space="preserve">Europace
@@ -809,8 +809,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】心室性不整脈はマルファン症候群で認識されることが増えていますが、関連する臨床的および構造的特徴は依然として不完全に定義されている (観察研究・その他 / N = 74例)
-【方法】われわれは、メイヨークリニックの3施設でマルファン症候群と確認された成人783人を対象に、後ろ向き多施設コホート研究を実施した。臨床データ、不整脈データ、心エコー検査データ、心臓磁気共鳴データ、外科データ、および植込み型除細動器のデータは、手作業によるカルテのレビューによって取得された。持続性心室頻拍（VT）または心室細動（VF）との関連性は、単変量ロジスティック回帰、全コホートの一次多変量モデル、および事前に指定された探索的心臓磁気共鳴感度モデルを使用してを評価した
-【結果】持続的な VT/VF は、12.7 ± 7.6 年間にわたって 74 人の患者 (9.5%) で発生しました。  単変量解析では、持続する VT/VF は、心房不整脈、心室リモデリング、僧帽弁疾患、心臓手術歴、遅発性ガドリニウム増強などの有害な構造電気的表現型と集中していました。  一次多変量モデルでは、非持続性心室頻拍（オッズ比、12.11 [95% CI、6.43-22.79]; &lt;0.001）、左心室駆出率低下（オッズ比、1% 増加あたり 0.95 [95% CI、0.93-0.97]; &lt;0.001）、少なくとも 1 回の心臓手術の病歴。 （オッズ比、3.59 [95% CI、1.65-7.84]; =0.001）および中等度から重度の僧帽弁逆流（オッズ比、2.00 [95% CI、1.07-3.75]; =0.030）は、持続性 VT/VF と独立して関連しました。 心臓磁気共鳴感度モデルでは、非持続性 VT、左心室駆出率下部、および後期ガドリニウム増強は依然として持続性 VT/VF と関連していました
+【方法】われわれは、メイヨークリニックの3施設でマルファン症候群と確認された成人783人を対象に、後ろ向き多施設コホート研究を実施した。
+【結果】持続的な VT/VF は、12.7 ± 7.6 年間にわたって 74 人の患者 (9.5%) で発生しました。
 【結論】マルファン症候群の成人では、持続性 VT/VF が患者 10 人に 1 人近くに発生し、より広範な構造電気表現型と関連している</t>
   </si>
   <si>
@@ -836,9 +836,9 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】植込み型除細動器（ICD）は以下の分野で使用されている (観察研究・その他 / N = 43例)
-【方法】25のHCMセンター（米国に8か所、ヨーロッパに9か所、アジアに4か所、オーストラリア、アフリカ、メキシコ、南米に各1か所）のデータベースを遡及的に調べて、ICDを伴うHCMの連続患者（1992年から2024年）を特定し、臨床転帰を7±6年間（最長32年間）追跡した
-【結果】合計 3,387 人の患者が特定された (63% が男性)。  それらの平均左心室厚さは２２±７ｍｍであった。  参加者は平均年齢47±17歳でICDを受けていました。  追跡調査では、550人の患者（16％）が1回以上の適切なICD療法（2.6％/年）を経験しており、その内訳は二次予防として埋め込まれた247人中86人（35％[6.4％/年]）、一次予防のために埋め込まれた3,140人中464人（15％[2.2％/年]）であった。  適切な治療を受けたのは平均年齢49±17歳の一次予防患者464名で、ICD移植後最初の適切な治療までの期間の中央値は4年であった。このうち 16% が移植後 10 年以上後に最初の適切な治療を受け、47% が複数回の介入を経験しました。 適切な ICD 治療の独立した予測因子には、外来モニタリングにおける原因不明の失神、左心室心尖動脈瘤、左心室収縮機能不全、および非持続性心室頻拍が含まれていました。  一次予防患者 3,140 人のうち、生存 2,946 人（94%）、死亡 194 人（6%）（0.8%/年）、このうち 68 人は HCM（0.3%/年）によるもので、主に末期心不全（n=43）または脳卒中（n=9）が原因であった。  対照的に、11 人の患者 (0.4%) が突然死亡し、生命を脅かす心室頻脈性不整脈のある患者の 2.4% で機器の故障が発生しました。  10年後および20年後のHCM関連死亡のない生存率は、それぞれ97%および91%であった
-【結論】この国際多施設研究は、HCMとICDの連続患者3,300人以上を含むこれまでで最大規模であり、機器治療により6人中1人の患者で致死性の可能性のある心室頻拍が停止し、ICD患者のHCM関連死亡率は低かった</t>
+【方法】25のHCMセンター（米国に8か所、ヨーロッパに9か所、アジアに4か所、オーストラリア、アフリカ、メキシコ、南米に各1か所）のデータベースを遡及的に調べて、ICDを伴うH…
+【結果】合計 3,387 人の患者が特定された (63% が男性)。
+【結論】この国際多施設研究は、HCMとICDの連続患者3,300人以上を含むこれまでで最大規模であり、機器治療により6人中1人の患者で致死性の可能性のある心室頻拍が停止し、ICD患者のHC…</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -855,9 +855,9 @@
 (Impact of Interelectrode Spacing on Ventricular Tachycardia Substrate Mapping: Insights Into 3-Dimensional Characteristics of the Arrhythmogenic Substrate.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】リエントラント心室頻拍 (VT) 回路には心内膜、心外膜、心筋中央部にわたる 3 次元の活性化が関与することが多く、包括的な基質評価の重要性が強調されている。電極間の間隔が広いと、従来の狭い間隔の記録では目立たなかった、より広いフィールドの電気コンポーネントを組み込むことができる。目的: この研究は、基質マッピングに対する電極間間隔の電気生理学的影響と、VT 基質の 3 次元特徴に対するその潜在的な影響を調査することを目的としました (観察研究・その他 / N = 35例)
-【方法】瘢痕関連 VT のカテーテル アブレーションを受けている 35 人の患者からの 68 枚の高密度基質マップを遡及的に分析しました。十極カテーテルを使用して、密な間隔 (2 mm) と広い間隔 (8 mm) の双極電位図を同時に取得し、密な間隔と広い間隔の双極電極マップ (CEM および WEM) を生成するために使用しました
-【結果】CEM と比較して、遠方界成分のより大きな寄与を組み込んだ WEM は、より高い双極性振幅、多成分心電図のより高い蔓延、および分割電位のより低い蔓延を実証しました (すべて P &lt; 0.01)。 CEM 上の分割電位によって描写されるブロックの線は、対応する電気記録図が断片化して見え、明確な分割構成を欠いているため、WEM では頻繁に減衰するか、または明白ではなくなりました。評価可能な活性化マップを使用した 6 つの VT の探索的分析では、活性化ギャップは、間隔が広い双極マッピングよりも狭い場合の方が大きかった (32.5% 対 20.0%; P = 0.03)。 4 つの VT では、間隔の広い記録により、狭い間隔の記録では明らかではなかった拡張期または収縮前遠方場電位が特定された
+    <t xml:space="preserve">【概要】リエントラント心室頻拍 (VT) 回路には心内膜、心外膜、心筋中央部にわたる 3 次元の活性化が関与することが多く、包括的な基質評価の重要性が強調されている。 (観察研究・その他 / N = 35例)
+【方法】瘢痕関連 VT のカテーテル アブレーションを受けている 35 人の患者からの 68 枚の高密度基質マップを遡及的に分析しました。
+【結果】CEM と比較して、遠方界成分のより大きな寄与を組み込んだ WEM は、より高い双極性振幅、多成分心電図のより高い蔓延、および分割電位のより低い蔓延を実証しました (すべて P &lt; 0.01)。
 【結論】VT 基板の 3 次元特徴について</t>
   </si>
   <si>
@@ -879,9 +879,9 @@
 (Pediatric Catecholaminergic Polymorphic Ventricular Tachycardia: Clinical Characteristics, Genetic Spectrum, and Outcomes in a Multicenter Cohort.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】カテコラミン作動性多形性心室頻拍 (CPVT) は、小児期に生命を脅かす心室性不整脈を引き起こすリスクが高い、まれな遺伝性不整脈である。目的：この研究は、小児CPVTの特徴を明らかにし、左心臓交感神経除神経（LCSD）および両側心臓交感神経除神経（BCSD）を含む現代の治療転帰を評価することを目的とした (観察研究・その他 / N = 25例)
-【方法】この後ろ向き多施設研究には、2012年から2025年までのトゥルキエの3つの三次センターからのCPVTの小児患者92人が含まれていた。不整脈事象には、中絶心停止、心臓突然死、適切な植込み型除細動器ショック、不整脈性失神、心室頻拍が含まれていた。適切な処置前観察期間を設けた患者において、対の処置前および処置後のイベント発生率を比較した
-【結果】症状発症時の年齢中央値は9.25歳（IQR：5.88～12.0）、診断時の年齢中央値は11.6歳（IQR：8.64～14.41）であった。遺伝子検査を受けた87人の患者のうち、74人（85.1％）が病原性または病原性の可能性のあるバリアントを持っていた。リアノジン受容体 2 とカルセクエストリン 2 の変異体は、それぞれ 41 名 (47.1%) と 24 名 (27.6%) で確認した。 50人の患者が交感神経の除神経を受けた(LCSD、n = 25; BCSD、n = 25)。ペアコホート（n = 35）では、不整脈イベント発生率の中央値は、LCSD/BCSD前の3.20イベント/年（IQR：1.74～8.76）から、術後の最初の2年間で0.00イベント/年（IQR：0.00～1.35）に減少しました（P &lt; 0.001）。最初の 2 年間のイベント発生率は、手順間で大きな差はなかった。 7人の患者が死亡した。文書化された治療不遵守は全員に存在した
+    <t xml:space="preserve">【概要】カテコラミン作動性多形性心室頻拍 (CPVT) は、小児期に生命を脅かす心室性不整脈を引き起こすリスクが高い、まれな遺伝性不整脈である。 (観察研究・その他 / N = 25例)
+【方法】この後ろ向き多施設研究には、2012年から2025年までのトゥルキエの3つの三次センターからのCPVTの小児患者92人が含まれていた。
+【結果】症状発症時の年齢中央値は9.25歳（IQR：5.88～12.0）、診断時の年齢中央値は11.6歳（IQR：8.64～14.41）であった。
 【結論】LCSD/BCSD は不整脈の負担の大幅な軽減と関連していましたが、観察による治療の割り当てと施設別の管理では、比較有効性に関する結論は得られません</t>
   </si>
   <si>
@@ -903,8 +903,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】および目的: パルスフィールドアブレーション (PFA) は治療にますます使用されている (観察研究・その他 / N = 22例)
-【方法】症候性発作性 (n = 22) および持続性 (n = 14) の AF を患う連続登録患者 36 人 (57 ± 11 歳、男性 69%) において、3D マッピングに基づいてこのカテーテルを使用して肺静脈隔離 (PVI) が実施した。 PVI の耐久性を確認するために、すべての患者が 3 か月後に再マッピングを受けました。患者は6ヵ月後と12ヵ月後に臨床レビュー、ホルターモニタリング、心電図検査を受けて追跡調査された。主要な有効性と安全性のエンドポイントには、12か月後の再発性AFの頻度が50%以上、7日と30日後の重篤な有害事象（SAE）の頻度が50%以上、6か月間のAFの頻度が60%を超えたことが含まれた
-【結果】すべてのエンドポイントは研究コホート全体で達成された。 SAE（保存的管理で回復した腎障害）は1件あり、総SAE率は2.8%であった。 1 人の患者は 12 か月時点で追跡不能となり、主要有効性評価項目は 92% (患者 35 人中 32 人) であった。二次有効性評価項目は、3 か月後の PVI が 82%、6 か月後の AF が 94% (患者 36 人中 34 人) であった。研究中、PFA 用量は 3 つのコホートで調整された。 「最適化されたサブセット」は、SAE がなく、6 か月および 12 か月の時点で 100% の PVI 耐久性と AF がなかった
+【方法】症候性発作性 (n = 22) および持続性 (n = 14) の AF を患う連続登録患者 36 人 (57 ± 11 歳、男性 69%) において、3D マッピングに…
+【結果】すべてのエンドポイントは研究コホート全体で達成された。
 【結論】発作性および持続性 AF のアブレーションのための新しい PFA カテーテル システムに関するこの研究は、あらかじめ定められた一次および二次臨床エンドポイントをすべて達成しました</t>
   </si>
   <si>
@@ -925,10 +925,10 @@
 (Clinical validation of an in silico pace mapping approach to localize both focal and re-entrant ventricular arrhythmias in patients with structural heart disease.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心室頻拍（VT）のカテーテルアブレーションは、処置時間が長く、再発が多いのが特徴である。パーソナライズされた画像ベースの計算モデルは、非侵襲性のアブレーションターゲットのガイダンスを提供する可能性がありますが、計算量が多く、焦点性不整脈の位置を特定することはできません。目的: この研究は、パーソナライズされた画像ベースのモデル内で焦点性およびリエントラント性不整脈の発生部位の両方を迅速に特定する、ほぼリアルタイムのインシリコペースマッピング (InSPM) アプローチを臨床的に検証することを目的としている (観察研究・その他 / N = 18例)
-【方法】瘢痕を組み込んだパーソナライズされたモデルは、構造的心疾患を患う 18 人の患者の画像データから再構築された。臨床ペース マッピング中に 12 誘導心電図 (ECG) が取得され、ペーシング部位の位置がグラウンド トゥルースとしてと定義した。誘発された単形性 VT の ECG テンプレートが取得された。仮想ペーシングはモデルで実行され、臨床テンプレートと関連付けられたシミュレートされた ECG により、高解像度の仮想ペースマップが作成された。臨床グラウンドトゥルースサイトとシミュレーションで予測されたターゲット領域の間の距離（d）は、最も高い相関を持ち、局所活性化のInSPM精度を定量的に評価しました。リエントラント VT については、予測されたターゲットを VT の起点部位およびマッピングされた VT 回路の代替物と比較しました
-【結果】臨床ペース マッピングの固有解像度は、同様に相関する ECG の場合、約 4 mm であった (平均相関係数 &gt; 0.99)。 270 の臨床ペースマッピング位置全体で、d は 8.2 mm (6.9 ～ 12 mm) で、心筋症の影響を比較的受けなかったが、右心室と左心室の精度は向上しました。特に虚血患者においては、患者固有の ECG 電極と正確な瘢痕表現が InSPM の精度を最適化するために重要であった。臨床 ECG VT テンプレートから作成された InSPM は、再入可能な VT 出口部位を確実に識別しました
-【結論】InSPM は、焦点 VT とリエントラント VT の両方を正確に位置特定するための、迅速かつ検証済みのパーソナライズされた計算モデリング アブレーション テクノロジーを提供し、実際に臨床ワークフローに統合できる</t>
+    <t xml:space="preserve">【概要】心室頻拍（VT）のカテーテルアブレーションは、処置時間が長く、再発が多いのが特徴である。 (観察研究・その他 / N = 18例)
+【方法】瘢痕を組み込んだパーソナライズされたモデルは、構造的心疾患を患う 18 人の患者の画像データから再構築された。
+【結果】臨床ペース マッピングの固有解像度は、同様に相関する ECG の場合、約 4 mm であった (平均相関係数 &gt; 0.99)。
+【結論】InSPM は、焦点 VT とリエントラント VT の両方を正確に位置特定するための、迅速かつ検証済みのパーソナライズされた計算モデリング アブレーション テクノロジーを提供し、実…</t>
   </si>
   <si>
     <t xml:space="preserve">Heart Rhythm
@@ -949,9 +949,9 @@
 (Left Stellate Ganglion Pulsed Radiofrequency Suppresses Ischemic Ventricular Arrhythmias: A Translational Study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】左星状神経節 (LSG) に由来する心臓の交感神経活動亢進は、虚血性心室不整脈 (VA) を引き起こしる。星状神経節ブロックは一時的な症状の軽減しか得られませんが、外科的除神経は侵襲的で不可逆的である。効果が持続する可能性のある、低侵襲性のアプローチが必要である。目的：この研究は、非熱的神経調節技術であるLSGのパルス高周波（PRF）が虚血性VAを安全に抑制するかどうかを調査し、統合された神経および心臓トランスクリプトミクスを使用してそのメカニズムを特徴付けることを目的とした (観察研究・その他 / N = 15例)
-【方法】安全性は、最初に、対照、LSG-PRF (42 °C、2 Hz、20 ミリ秒)、または外科的 LSG 切除に無作為化された健康なラット (n = 15) で評価した。ラット心筋梗塞（MI）モデル（n = 24; Sham、MI、MI + PRF）では、心臓交感神経活動、プログラムされた電気刺激、心エコー検査、および組織学が評価され、LSG のバルク RNA 配列および心臓組織の単一細胞 RNA 配列によって補完された。超音波ガイド下の LSG-PRF を使用して、薬剤抵抗性の電気嵐を患う 4 人の患者でトランスレーショナルの実現可能性をテストしました
-【結果】LSG切除とは対照的に、PRFは一過性のホルネル症候群のみを引き起こし、低血圧を引き起こしなかった。  MI ラットでは、PRF は心臓交感神経活動を低下させ、心室頻拍/心室細動の誘導性とプログラム刺激の継続時間を軽減し、血清ノルエピネフリンとアンジオテンシン II を低下させ、左心室機能を改善し、心筋線維症を軽減しました。  LSG トランスクリプトミクスにより、S100a9 や Ngf などの炎症および発芽関連遺伝子の下方制御が示した。  梗塞した心臓の単細胞解析により、炎症誘発性のGrik2シュワン細胞サブセットが減弱しており、計算上、神経免疫シグナル伝達が減少していることが明らかになった。 4 人の患者全員において、中央値 12 か月の追跡調査中に持続性心室頻拍の再発は観察されなかった
+    <t xml:space="preserve">【概要】左星状神経節 (LSG) に由来する心臓の交感神経活動亢進は、虚血性心室不整脈 (VA) を引き起こしる。 (観察研究・その他 / N = 15例)
+【方法】安全性は、最初に、対照、LSG-PRF (42 °C、2 Hz、20 ミリ秒)、または外科的 LSG 切除に無作為化された健康なラット (n = 15) で評価した。
+【結果】LSG切除とは対照的に、PRFは一過性のホルネル症候群のみを引き起こし、低血圧を引き起こしなかった。
 【結論】LSG-PRF は、神経節炎症の軽減と心臓神経免疫シグナル伝達の調節を伴う、交感神経活動亢進および MI 後の VA の抑制に関連する低侵襲性の神経調節戦略である</t>
   </si>
   <si>
@@ -969,9 +969,9 @@
 (Impact of pulsed field ablation on ganglionated plexi function in atrial fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】熱エネルギーを使用する肺静脈隔離 (PVI) は、左心房 (LA) 神経節叢 (GP) への付随損傷を介して抗不整脈効果の一部を発揮する可能性がありる。心内膜パルスフィールドアブレーション (PFA) は心臓選択的になるように設計されていますが、ヒトの GP 機能に対するその影響は不明である。目的: この研究は、LA GP 活動に対する心内膜 PFA の影響を系統的に評価することを目的としました (観察研究・その他 / N = 10例)
-【方法】この前向きコホート研究では、初めて PFA を受けた持続性心房細動患者が連続して登録された。心房細動中の局所高周波刺激により、房室遅延（AVD）（AVD-GP）を示すLA GP部位が特定された。これは、高周波刺激中の50％以上のRR延長または心停止として定義される。後壁アブレーションを伴う PVI を達成するために、ペンタスプライン カテーテルを使用して広範な前庭 PFA を送達しました。 PFA 病変を覆う AVD-GP 部位を含むセグメントが再検査され、その後、活性な AVD-GP 部位が高周波 (RF) アブレーションで標的化され、再を評価した
-【結果】10人の患者(年齢61.9±7.1歳、女性3人[30%])が登録された。ベースラインでは、検査された591部位のうち118部位(20.0%)がAVD-GP基準(患者当たり11.8±7.8)を満たしており、これには肺静脈口の23部位(19.5%)が含まれていた。一過性 AVD は、PFA 適用中に患者 10 人中 4 人 (40%) で発生しました。 PFA 後、PFA 治療領域を覆う AVD-GP 部位を有する 21 セグメントのうち 16 セグメント (患者あたり 2.0 ± 1.1 セグメント) が持続的な AVD 反応を示しました。ターゲットを絞った RF アブレーションの後、以前に活性だった AVD-GP 部位は AVD 応答を示さなくなりました
+    <t xml:space="preserve">【概要】熱エネルギーを使用する肺静脈隔離 (PVI) は、左心房 (LA) 神経節叢 (GP) への付随損傷を介して抗不整脈効果の一部を発揮する可能性がありる。 (観察研究・その他 / N = 10例)
+【方法】この前向きコホート研究では、初めて PFA を受けた持続性心房細動患者が連続して登録された。
+【結果】10人の患者(年齢61.9±7.1歳、女性3人[30%])が登録された。
 【結論】心内膜ＰＦＡは、重複部位への病変送達にもかかわらず、一貫してＬＡ ＧＰ機能を消失させるわけではない</t>
   </si>
   <si>
@@ -994,8 +994,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】カテーテルアブレーションは、小児および先天性心疾患（CHD）における頻脈性不整脈に対する効果的かつ安全な治療法であることが証明されている (観察研究・その他 / N = 3例)
-【方法】記述的かつ分析的なレトロスペクティブ観察研究が実施した。 6 か月間利用できるクローズド コード化されたオンライン フォームが使用された。ラテンアメリカで小児電気生理学を実践し、以前の LAHSR の調査で特定された電気生理学者全員が、ラテンアメリカ心調律協会 (LAHRS) 電子メディア ( https://lahrs.org/ ) を通じて参加するよう招待された。参加は強制ではなく、経済的または物質的な財によって奨励されるものではなく、データの使用についてのインフォームドコンセントが必要であった。 2017年から2021年まで、年齢に関係なく、18歳未満の小児またはCHD患者を対象に、連続電気生理学的カテーテル処置が行いた
-【結果】ラテンアメリカ8カ国から20人の医師が参加した。  合計1,778件の手術が報告され、53％が男性、平均年齢は12.4±5.1歳、8.5％が先天性心疾患を患っていた。  患者の 87% でアブレーションが試みられ、そのうちの 68% では非灌流先端高周波カテーテルが使用され、29% では 3D マッピング システムが使用された。  98% のケースで最も一般的に使用されたエネルギー源は高周波であった。  最も頻度の高い基質は副経路で 69.5% (61% が明示的)、次いで房室結節リエントリーが 16.5%、異所性心房頻脈が 4% であった。  さらに、心房粗動が 3.8%、心室頻拍が 3.8%、心室性期外収縮が 1.2% 発生しました。  症例の 93% でアブレーションは直ちに成功したと考えられる。 平均総処置時間は 92.1 ± 36.8 分、平均総透視時間は 16.3 ± 9.4 分であった。  合併症率は 1.8% で、3 人の患者 (0.2%) には完全な房室ブロックが含まれていました。  死亡者は報告されていない。  再発率は8.5%であった
+【方法】記述的かつ分析的なレトロスペクティブ観察研究が実施した。
+【結果】ラテンアメリカ8カ国から20人の医師が参加した。
 【結論】ラテンアメリカにおけるこの初の小児および先天性心疾患のみを対象としたカテーテルアブレーションの遡及的登録では、高い成功率と低い合併症発生率が認めた</t>
   </si>
   <si>
@@ -1014,8 +1014,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】定位性不整脈放射線アブレーション (STAR) は、難治性心室頻拍に対する有望な非侵襲的治療法である (観察研究・その他 / N = 2例)
-【方法】6 頭のブタ (最初の 2 頭はプロトコルのテストとして使用) は、治療計画のために左心室自由壁の心筋標的に 35 Gy の単回分割線量でベースライン CT を受けました。その後、走査陽子線を使用したシングルゲートまたはデュアルゲート送達で治療された。治療反応は、ベースライン時および照射後 14 ～ 15 週間目に、心エコー検査、血液分析、陽電子放出断層撮影 (PET)-CT によってを評価した。終了時に病変を評価し、組織を病理組織学のために採取した
-【結果】フラクショナル モーションの平均ターゲット拡張は、シングル ゲートと比較してデュアルの方が低かった (16% ～ 23% 対 48% ～ 72%、各アームで N = 2)。照射領域は、すべての動物において、PET-CT では in vivo で、また ex vivo の剖検では予想された位置で識別可能であった。視覚的病変の貫壁性は組織学によって確認された。病変サイズは、デュアルゲート動物では予想される体積からそれほど遠くなかったが、シングルゲート動物では大きかった（グループ間の比較では p = 0.3、各アームで N = 2）
+【方法】6 頭のブタ (最初の 2 頭はプロトコルのテストとして使用) は、治療計画のために左心室自由壁の心筋標的に 35 Gy の単回分割線量でベースライン CT を受けました…
+【結果】フラクショナル モーションの平均ターゲット拡張は、シングル ゲートと比較してデュアルの方が低かった (16% ～ 23% 対 48% ～ 72%、各アームで N = 2)。
 【結論】より、ワークフローの実現可能性が確認した</t>
   </si>
   <si>
@@ -1033,9 +1033,9 @@
 (Safety and performance of vibration-assisted extraction of chronic cardiac implantable electronic device leads: A preclinical ovine study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】慢性心臓植込み型電子機器リードの経静脈的抜去には、線維性癒着や処置上のリスクが伴いる。新しい技術は安全性と有効性の向上を目指している。高周波機械振動システムは、癒着を破壊することを目的としている。目的: この研究は、前臨床適正実験基準ヒツジモデルにおける新しい振動補助リード抽出システムの初期の安全性、性能、および使いやすさを評価することを目的としました (観察研究・その他 / N = 2例)
-【方法】2 年以上（範囲 2.9 ～ 5.25 年）埋め込まれた 9 本のリードが、蛍光透視下で振動システムを使用して 6 頭の羊から抽出された。リードの内腔は、カスタマイズされたロッキング スタイレットを送達するために使用された。スタイレットを使用してリードに振動エネルギーを与え、1 匹あたり最大 20 分間適用しました。評価には、手術の成功、リードの完全性、手術中のモニタリング、3日間の臨床フォローアップ、臨床検査、剖検、および病理組織学（心臓、肺、中心静脈）が含まれる
-【結果】補助器具を使用しない場合、手術の成功率 (リード除去) は 100% であった。すべての症例で癒着剥離に外部切断シースは必要なかった。リードの解放は、9 つ​​のリードのうち 8 つで約 1 分以内に発生しました。主要な安全性評価項目は満たされた：中心静脈または心筋穿孔がないこと、および肺塞栓症がないこと。血圧低下、重大な不整脈、三尖弁逆流の悪化は発生しなかった。 1 つのリード骨折 (9 件中 1 件) では、軽度の局所的な心筋壊死を伴う遠位スクリューの残存 (&lt;1 cm) が発生しました。アンカーデバイスの誤動作により、2 件のケースで処置中の交換が必要になりました
+    <t xml:space="preserve">【概要】慢性心臓植込み型電子機器リードの経静脈的抜去には、線維性癒着や処置上のリスクが伴いる。 (観察研究・その他 / N = 2例)
+【方法】2 年以上（範囲 2.9 ～ 5.25 年）埋め込まれた 9 本のリードが、蛍光透視下で振動システムを使用して 6 頭の羊から抽出された。
+【結果】補助器具を使用しない場合、手術の成功率 (リード除去) は 100% であった。
 【結論】このヒツジモデルでは、慢性心臓植込み型電子機器リードの振動支援による抜去が可能であり、主要な安全性エンドポイントを満たし、顕著な急性安全性プロファイルを示しました</t>
   </si>
   <si>
@@ -1056,9 +1056,9 @@
 (Feasibility, Safety, and Efficacy of Pulsed Field Ablation for Ventricular Arrhythmias: Insights From a Large Health System Registry in the United States.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房性不整脈アブレーションにおける安全性が証明されている新興の非熱的アブレーションモダリティである。ただし、心室性不整脈 (VA) に対するその性能に関するデータは依然として限られている。目的: 現実世界の米国多施設登録における複雑な VA に対する PFA の実現可能性、安全性、有効性を評価すること (観察研究・その他 / N = 1例)
-【方法】この後ろ向き研究には、メイヨークリニックの3つのセンターで心室頻拍（VT）または心室性期外収縮（PVC）のPFAを受けた連続患者が含まれた（2024年4月から2025年7月まで）。主要な実現可能性の成果は、意図した標的基質への PFA 損傷の送達の成功であった。主な有効性アウトカムには、急性処置の成功が含まれる。植込み型除細動器（ICD）ショックまたは複数回の抗頻脈ペーシング療法を必要とする持続的な心室頻拍再発。 PVC 負荷が 80% 以上削減される。安全性の結果には、処置上の合併症、弁機能、血栓塞栓性イベント、腎機能、伝導障害が含まれる
-【結果】26 人の患者が含まれました (PVC 13 人、VT 13 人)。すべての VT アブレーション (69.2% が完了、30.8% が部分的) および 92.3% の PVC アブレーションで急性成功が達成された。合併症は患者の 11.5% で発生しました (一過性 LBBB [n = 1] および血管合併症 [n = 2])。血栓塞栓性イベント、心臓内血栓、または急性腎損傷は観察されなかった。僧帽弁装置付近の病変は、既存の弁膜症患者を含め、僧帽弁逆流を悪化させなかった。中央値365日の追跡調査の後、1人の患者がICDショックを必要とするVT再発を経験した。 VT アブレーション後の推定無再発生存率は 12 か月時点で 61.5% であった。 PVC 患者の 58.3% が 80% 以上の負担軽減を達成しました
+    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房性不整脈アブレーションにおける安全性が証明されている新興の非熱的アブレーションモダリティである。 (観察研究・その他 / N = 1例)
+【方法】この後ろ向き研究には、メイヨークリニックの3つのセンターで心室頻拍（VT）または心室性期外収縮（PVC）のPFAを受けた連続患者が含まれた（2024年4月から2025年7…
+【結果】26 人の患者が含まれました (PVC 13 人、VT 13 人)。
 【結論】VA に対する PFA は実行可能であり、非常に効果的であり、処置に関連した合併症の発生率は低いと考えられる</t>
   </si>
   <si>
@@ -1138,10 +1138,10 @@
 (Atrial Fibrillation Ablation Effectiveness End Points, Safety End Points, and Trial Design: Academic Research Consortium Initiative Endorsed by the Heart Rhythm Society.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】AFA-ARC (心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討し、規制上の意思決定をサポートする意味のある解釈可能なデータを提供することである (観察研究・その他 / 症例数: 不明)
-【方法】2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または別々に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行いた
-【結果】このプロセスの主要な部分は、心房細動のカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討するための統合文書の作成であった。この文書は、3 つの作業グループのそれぞれからの貢献を表している。 Heart Rhythm Society はこの文書を承認しました。このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂版を提案している
-【結論】このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂版を提案している</t>
+    <t xml:space="preserve">【概要】AFA-ARC (心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試… (観察研究・その他 / 症例数: 不明)
+【方法】2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、…
+【結果】このプロセスの主要な部分は、心房細動のカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討するための統合文書の作成であった。
+【結論】このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂…</t>
   </si>
   <si>
     <t xml:space="preserve">Circ Arrhythm Electrophysiol
@@ -1158,10 +1158,10 @@
 (Left Atrial Voltage Attenuation Beyond Ablation Sites After Unipolar Pulsed-Field Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広範囲の電場を生成する可能性がありる (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に… (観察研究・その他 / 症例数: 不明)
 【方法】そして
-【結果】私たちは、Affera システムを使用して原発性心房細動アブレーションを受けた連続 5 人の患者を遡及的に研究しました。  アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webster) を使用して、右心房ペーシング中に同一の設定で生成された。  Affera には空間マッチングのためのポイントレベルの 3D 座標がないため、座標 (x、y、z) と双極電圧は CARTO 3 から抽出された。エネルギー伝達部位の外側のアブレーション前後のポイント (線維輪と左心耳を除く) は、2 mm の相互最近傍基準を使用して空間的にマッチングされた。  これにより、3772 ペアが得られました。  双極性電圧はケースごとに平均化された。 平均双極電圧はすべての場合で 1.01 ± 0.61 から 0.56 ± 0.29 mV に減少し、40.2% の減少を示しました (95% CI、24.6%-55.8%、p = 0.044)。  距離階層化分析では、残留双極電圧（事後/事前×100）は、アブレーションゾーンの直後で最も低く、最も近いアプリケーションタグ中心からの距離に応じて徐々に増加し（10〜15 mmで16.5%、25〜30 mmで57.8%、すべてp&lt;0.001）、約30 mmを超えると数値的にベースラインと同等になりました
-【結論】アフェラベースの単極アブレーションでは、急性双極電圧減衰が発生し、病変セットに隣接する非アブレーション心筋層まで広がりましたが、距離とともに減少し、大部分は適用部位の約 30 mm 以内に限定されていました</t>
+【結果】私たちは、Affera システムを使用して原発性心房細動アブレーションを受けた連続 5 人の患者を遡及的に研究しました。
+【結論】アフェラベースの単極アブレーションでは、急性双極電圧減衰が発生し、病変セットに隣接する非アブレーション心筋層まで広がりましたが、距離とともに減少し、大部分は適用部位の約 30 mm…</t>
   </si>
   <si>
     <t>Osaki S, Inoue K, Mishima T, Ozaki T, Ohashi T, Abe H, et al.. Left Atrial Voltage Attenuation Beyond Ablation Sites After Unipolar Pulsed-Field Ablation for Atrial Fibrillation.. J Cardiovasc Electrophysiol. 2026 Sep 27;:. doi: 10.1111/jce.70511 doi.</t>
@@ -1174,9 +1174,9 @@
 (Learning Curve of Pentaspline Pulsed-Field Ablation With Posterior Wall Isolation for Persistent Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままである (観察研究・その他 / 症例数: 不明)
-【方法】われわれは、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。急性不完全病変は、体系的な再マッピング後に追加の PFA 適用を必要とする残留伝導としてと定義した。学習フェーズは、セグメント化されたロジスティック回帰と逐次ブロック分析を使用して特定された。多変数モデルは、処置期、左心房容積 (LAV)、および後壁の形状を評価しました
-【結果】学習曲線が観察され、最初の 20 回の処置中に不完全な病変形成が最も減少しました。不完全病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました。手術段階は不完全病変の主な決定要因であり、初期段階と中期段階ではそれぞれ約 24 倍と 9 倍高いオッズであった。より大きな LAV は、適度な独立した関連性 (OR 1.009/mL) を示しましたが、後壁の形状は独立した関連性を示しなかった。中期の不整脈再発は各期で差はなかったが、後期では追跡期間が短かった
+    <t xml:space="preserve">【概要】ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法と… (観察研究・その他 / 症例数: 不明)
+【方法】われわれは、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。
+【結果】学習曲線が観察され、最初の 20 回の処置中に不完全な病変形成が最も減少しました。
 【結論】PVI + PWI を使用したペンタスプライン PFA 中の病変の完全性は、処置の経験が増えるにつれて徐々に向上しる</t>
   </si>
   <si>
@@ -1214,8 +1214,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】覚醒剤はADHDに対して広く処方されている。一般に安全だと考えられていますが、 (観察研究・その他 / 症例数: 不明)
-【方法】心房および心室の hiPSC-CM を多電極アレイ (MEA) プラットフォーム上にプレーティングし、臨床的に関連する血漿濃度のメチルフェニデート、デキストロアンフェタミン、アトモキセチン、カフェイン、または β アゴニストのイソプロテレノールに曝露しました。細胞外電場電位を 48 時間にわたって記録し、伝導速度 (CV)、心拍数 (BR)、および補正電場電位持続時間 (FPDc) に対する急性および長期の影響を評価しました
-【結果】心房および心室の両方の hiPSC-CM では、CV はすべての刺激条件にわたってほぼ維持されたが、イソプロテレノールは初期にわずかな増加を示しました。すべての興奮剤は、暴露の最初の 1 時間に BR を一時的に上昇させ、その後、時間の経過とともに徐々に低下しました。イソプロテレノールとカフェインは BR の強力かつ持続的な増加を誘導し、モデルの応答性を確認しました。 FPDc は、既知の I 阻害特性と一致して、すべての刺激化合物によって延長されたが、最も顕著なのはアトモキセチンによって延長された。イソプロテレノールは、特に hiPSC-vCM において速度依存的な FPDc 短縮を引き起こしました
+【方法】心房および心室の hiPSC-CM を多電極アレイ (MEA) プラットフォーム上にプレーティングし、臨床的に関連する血漿濃度のメチルフェニデート、デキストロアンフェタミ…
+【結果】心房および心室の両方の hiPSC-CM では、CV はすべての刺激条件にわたってほぼ維持されたが、イソプロテレノールは初期にわずかな増加を示しました。
 【結論】臨床的に適切な血漿濃度では、刺激剤は自動性と再分極を調節しますが、hiPSC-CM の伝導には最小限の影響しか与えなかった</t>
   </si>
   <si>
@@ -1233,10 +1233,10 @@
 (Monitored anesthesia care versus general anesthesia for balloon-in-basket pulsed-field ablation of atrial fibrillation: an age-matched analysis of procedural timing and acute procedural outcomes.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】米国では、全身麻酔（GA）が心房細動（AF）カテーテルアブレーションの鎮静戦略として好まれている。これは、パルスフィールドアブレーション（PFA）システムが骨格筋の刺激と不快感を引き起こし、軽い鎮静下では耐えられないことが部分的に理由となっている。最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性がありる。この状況において、MAC がアブレーションの有効性を損なうことなく手技効率の利点を提供するかどうかは、十分に特徴づけられていません。目的: MAC と GA の間で処置のタイミング、アブレーションの有効性、安全性をの比較 (観察研究・その他 / 症例数: 不明)
-【方法】我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。  各 MAC 患者は、利用可能な最も近い年齢の GA 患者と 1:1 でマッチングされ、39 人の年齢が一致した対照が得られました。  6 つの異なる時間間隔が収集された: 総室時間、処置前のセットアップ時間、中心処置時間、処置後のターンオーバー時間、経中隔から左心房 (LA) へのシースアウト (滞留) 時間、およびアブレーション カテーテルの滞留時間。  施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較された。  次に、グループ比較が行った。 さらに、公開されている EP/手順スイートの 1 分あたりのコスト見積もりを使用して、観察された総室内時間の違いに関連する EP 検査施設のコスト削減とスケジュールの機会コストも決定された
-【結果】総室時間 (103.5 ± 20.0 対 126.2 ± 33.1 分; p = 0.0004)、処置前の準備時間 (33.4 ± 10.0 対 50.3 ± 28.0 分; p = 0.0007)、および処置後のターンオーバー時間 (14.8 ± 9.3 対 21.4) ± 8.3 分、p = 0.0030) は MAC の方が有意に短かった。  コア処置時間（55.3 ± 20.5 対 55.3 ± 23.9 分）、経中隔から LA シースアウト時間（34.2 ± 12.9 対 35.7 ± 18.5 分）は、グループ間で有意な差はなかった（両方 p ≥ 0.62）。  アブレーションカテーテルの滞留時間は、MAC の方が若干長くなりました (27.7 ± 11.9 対 24.2 ± 15.5 分; p = 0.036)。  施行された総切除病変数（17.6 ± 5.1 対 18.8 ± 7.2、p = 0.68）および急性処置成功率（39/39 [100%] 対 39/39 [100%]）は、MAC 群と GA 間で同様であり、どちらのグループにも処置上の合併症はなかった。 MAC 症例 1 例 (2.6%) は、気道分泌物による咳のため、処置の途中で全身麻酔に変更された。  公表されている EP/手続きスイートの 1 分あたりのコスト見積もり (29 ドルから 60 ドル/分) を、観測された合計在室時間の 22.7 分の削減に適用すると、MAC は 1 件あたりの設備コストの推定 658 ドルから 1,362 ドルの節約に関連しており、追加のケースのスケジュール設定による潜在的な機会費用の利点が見られました
-【結論】AFのためにBiB PFA（VOLT）を受けた年齢を一致させたコホートでは、MACはGAよりも総室時間、処置前の準備時間、および処置後の回転時間の短縮と関連しており、アブレーション病変の送達、急性成功、または合併症には差がなかった</t>
+    <t xml:space="preserve">【概要】米国では、全身麻酔（GA）が心房細動（AF）カテーテルアブレーションの鎮静戦略として好まれている。 (観察研究・その他 / 症例数: 不明)
+【方法】我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。
+【結果】総室時間 (103.5 ± 20.0 対 126.2 ± 33.1 分; p = 0.0004)、処置前の準備時間 (33.4 ± 10.0 対 50.3 ± 28.0 分; p = 0.0007)、および処置後のターン…
+【結論】AFのためにBiB PFA（VOLT）を受けた年齢を一致させたコホートでは、MACはGAよりも総室時間、処置前の準備時間、および処置後の回転時間の短縮と関連しており、アブレーション…</t>
   </si>
   <si>
     <t>Sundaram S, Palmeri N, Alyesh D, Cerbin L, Sundaram K, Rappaport A, et al.. Monitored anesthesia care versus general anesthesia for balloon-in-basket pulsed-field ablation of atrial fibrillation: an age-matched analysis of procedural timing and acute procedural outcomes.. J Interv Card Electrophysiol. 2026 Sep 25;:. doi: 10.1007/s10840-026-02443-2 doi.</t>
@@ -1292,10 +1292,10 @@
 (Efficacy and Safety of 60 W Versus 90 W, 4-s Radiofrequency Applications to the Esophagus-Adjacent Left Atrial Posterior Wall During Pulmonary Vein Isolation: A Pilot Study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】QDOT MICRO カテーテルを使用した非常に高出力 (51 ～ 90 W)、短時間 (4 秒) の高周波アプリケーション (QMODE+) では、心房細動 (AF) を治療するための食道に隣接する左心房 (LA) 後壁での最適な出力設定は不明のままである。目的: 食道周囲領域における 60 W と 90 W の QMODE+ 高周波アプリケーションの有効性と安全性を評価しました (観察研究・その他 / 症例数: 不明)
-【方法】50 人の AF 患者は、食道周囲領域に適用される QMODE+ 出力に基づいて、60 W (= 24) と 90 W (= 26) の 2 つのグループに無作為にに割り付けた。食道周囲領域および内視鏡的食道病変における残存伝導ギャップの発生率、および 2 つのグループ間の 1 年心房性頻脈性不整脈 (AT) 再発率を比較しました
-【結果】接触力の中央値は、90 W グループよりも 60 W グループの方が有意に高かった (60 W グループでは 12.9 g [IQR 10.2、15.8]、90 W グループでは 10.9 g [IQR 8.4、14.2]、&lt; 0.001)。残存伝導ギャップ率 (それぞれ 8.3% と 11.5% = 1.00) および食道病変 (各グループの 4.2%) の割合は 2 つのグループ間で同様であった。 1 年 AT 再発率は 2 つのグループ間で有意な差はなかった (それぞれ 20.8% 対 7.7% = 0.24)
-【結論】食道周囲領域への 60 W および 90 W QMODE+ RF アプリケーションでは、急性伝導ブロック、内視鏡検査で検出された食道損傷、および 12 か月の AT 無再発生存率が同等の率を達成しましたが、接触力は 60 W グループの方が有意に高かったである</t>
+    <t xml:space="preserve">【概要】QDOT MICRO カテーテルを使用した非常に高出力 (51 ～ 90 W)、短時間 (4 秒) の高周波アプリケーション (QMODE+) では、心房細動 (AF) … (観察研究・その他 / 症例数: 不明)
+【方法】50 人の AF 患者は、食道周囲領域に適用される QMODE+ 出力に基づいて、60 W (= 24) と 90 W (= 26) の 2 つのグループに無作為にに割り…
+【結果】接触力の中央値は、90 W グループよりも 60 W グループの方が有意に高かった (60 W グループでは 12.9 g [IQR 10.2、15.8]、90 W グループでは 10.9 g [IQR 8.4、14.2…
+【結論】食道周囲領域への 60 W および 90 W QMODE+ RF アプリケーションでは、急性伝導ブロック、内視鏡検査で検出された食道損傷、および 12 か月の AT 無再発生存率が…</t>
   </si>
   <si>
     <t xml:space="preserve">J Arrhythm
@@ -1331,9 +1331,9 @@
 (Effect of Pulsed Field Timing Sequence and Electrode Cooling on Ablation Safety and Efficacy Surrogates: A Preclinical Study.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】可変ループ円形カテーテルは、心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されている。初期波形 (Seq1) の商用発売後、電極表面温度とアブレーション送達時間 (20 ～ 3.8 秒) を短縮する新しい波形 (Seq2) が開発された。この研究では、2 つの洗浄速度と 2 つの投与条件にわたって、Seq1 と Seq2 の安全性と有効性を比較しる (観察研究・その他 / 症例数: 不明)
-【方法】24 頭のヨークシャー豚を、可変ループ円形カテーテルを使用したパルスフィールド アブレーションで治療しました。被験者は、3 つのパルス レシピ/灌注アーム (Seq1、Seq1、および Seq 2) に無作為にに割り付けた。各グループは、名目上の 1 倍の用量グループと 2 倍の用量のグループに分割された
-【結果】すべてのグループにおいて、側副傷害の証拠のない経壁性、周囲性、肺静脈病変によって示されるように、急性および慢性肺静脈隔離効果が 100% を認めた。左心耳、LA屋根、および後壁における貫壁性は、すべてのグループにわたって75%〜100%であり、僧帽弁峡部には存在しなかった。 Seq2 または Seq1 ではカテーテル血栓/炭化物は観察されなかった。 Seq1 では、血栓/炭化物が 25% (1x) と 100% (2x) で発生しました。溶血および心筋損傷マーカーの変化はすべてのグループ間で同様であったが、2x グループで顕著に増加しました。心エコー検査では、Seq2 のマイクロバブルはほとんどまたはまったくないとを評価したが、Seq1 と Seq1 はほとんどが中程度またはシャワー程度とを評価した
+    <t xml:space="preserve">【概要】可変ループ円形カテーテルは、心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されている。 (観察研究・その他 / 症例数: 不明)
+【方法】24 頭のヨークシャー豚を、可変ループ円形カテーテルを使用したパルスフィールド アブレーションで治療しました。
+【結果】すべてのグループにおいて、側副傷害の証拠のない経壁性、周囲性、肺静脈病変によって示されるように、急性および慢性肺静脈隔離効果が 100% を認めた。
 【結論】両方の投与条件にわたって、Seq1、Seq2、および Seq1 を含むすべてのグループにわたって、一貫して耐久性のある肺静脈隔離が認めた</t>
   </si>
   <si>
@@ -1351,9 +1351,9 @@
 (PFKFB2 Gates a Relationship Between Cardiac Glycolytic Regulation and Electrophysiological Function.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】PFKFB2 の心臓アイソフォーム (ホスホフルクトキナーゼ-2/フルクトース 2,6-ビスホスファターゼ) は心臓の最も強力な解糖調節因子ですが、インスリンシグナル伝達がないと分解される。このため、インスリンシグナル伝達の障害が特徴である代謝性心疾患では、PFKFB2 欠損を理解することが重要となる。 QT間隔の延長、不整脈のリスク、心臓突然死も代謝性心疾患で増大しており、解糖系調節障害と電気生理学的機能障害との間にクロストークが存在するかどうかという疑問が生じている (観察研究・その他 / 症例数: 不明)
-【方法】したがって、我々は、心筋細胞特異的 PFKFB2 ノックアウト マウス モデル (cKO) と同腹仔の対照を使用して、心臓電気生理学に対する PFKFB2 欠損の影響を評価しました。そのために、我々は、摂食状態および12時間の絶食後の心電図検査を採用し、ベースラインと急性刺激性ストレスの存在下の両方で生理機能を調べました。不整脈のメカニズムをさらに調査するために、パッチクランプ電気生理学と、対照心臓およびcKO心臓から単離した心室心筋細胞におけるIonOptix Ca過渡測定を使用しました
-【結果】cKO マウスの心臓は、QT および活動電位持続時間の延長を特徴とする長期の再分極を示しました。これは、心室心筋細胞における Ca 再取り込みの障害と自発的 Ca 放出事象の増加によって起こりました。後者は、cKO心臓の摂食状態で増強される翻訳後修飾であるO-GlcNAc化を介して上方制御された。最終的に、これらの変化は cKO マウスの心室頻脈性不整脈を引き起こし、絶食状態に比べて食餌状態で増強された
+    <t xml:space="preserve">【概要】PFKFB2 の心臓アイソフォーム (ホスホフルクトキナーゼ-2/フルクトース 2,6-ビスホスファターゼ) は心臓の最も強力な解糖調節因子ですが、インスリンシグナル伝達… (観察研究・その他 / 症例数: 不明)
+【方法】したがって、我々は、心筋細胞特異的 PFKFB2 ノックアウト マウス モデル (cKO) と同腹仔の対照を使用して、心臓電気生理学に対する PFKFB2 欠損の影響を評…
+【結果】cKO マウスの心臓は、QT および活動電位持続時間の延長を特徴とする長期の再分極を示しました。
 【結論】これらのデータは、十分なグルコース利用可能性の存在下では、ホスホフルクトキナーゼ結合における心臓の解糖調節異常が心臓の電気生理学的不安定性を促進するのに十分であることを示唆している</t>
   </si>
   <si>
@@ -1411,9 +1411,9 @@
 (Targeting trafficking defects in long QT syndrome type 2: a phase 2 clinical study with patient-specific cellular validation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】および目的: QT 延長症候群 (LQTS) の主な構成要素は、KCNH2 の病原性変異による LQT2 であり、これは頻繁に輸送欠陥を引き起こしる。治療管理の進歩にもかかわらず、メカニズムを標的とした治療に対する臨床上のニーズは満たされていません。患者特異的なヒト人工多能性幹細胞由来心筋細胞（hiPSC-CM）を用いて、現在嚢胞性線維症に使用されているルマカトール（LUM）がhERG輸送を部分的に修正できることが以前に示されている。 LUM が LQT2 の QTc を短縮できるかどうかを判断するために、単群フェーズ 2 試験が実施した (観察研究・その他 / 症例数: 不明)
-【方法】遺伝子的に輸送欠陥KCNH2変異体が確認された成人患者16名が登録された。参加者は入院し、連続遠隔測定下で 7 日間 LUM の投与を受けました。 QTc は、連続心電図と 12 誘導ホルター記録で定量化された。機構的な相関関係を調べるために、異なる遺伝子変異を持つ最初の 5 人の参加者から hiPSC-CM を生成し、hERG の成熟と輸送について評価しました
-【結果】全体として、lumacaftor は有意な QTc 短縮をもたらしました (P &lt; 0.001)。患者ごとの変化は平均 31 ± 21 ミリ秒であった。ベースライン QTc が 500 ミリ秒以上の患者が最も大きな効果を示し、75% が 40 ミリ秒以上の減少を達成しました。心室性不整脈は発生せず、副作用は主に胃腸であり、自然に限定された。 hiPSC-CM では、LUM は 5 つの変異体のうち 3 つで hERG 輸送を回復させ、臨床観察を反映しました
+    <t xml:space="preserve">【概要】および目的: QT 延長症候群 (LQTS) の主な構成要素は、KCNH2 の病原性変異による LQT2 であり、これは頻繁に輸送欠陥を引き起こしる。 (観察研究・その他 / 症例数: 不明)
+【方法】遺伝子的に輸送欠陥KCNH2変異体が確認された成人患者16名が登録された。
+【結果】全体として、lumacaftor は有意な QTc 短縮をもたらしました (P &lt; 0.001)。
 【結論】短期 LUM 療法は安全であり、輸送欠陥のある LQT2 患者において大幅な QTc 短縮をもたらしる</t>
   </si>
   <si>
@@ -1434,10 +1434,10 @@
 (Sphingomyelin as a key negative mediator in atrial fibrillation via lipid proﬁling analysis and functional identiﬁcation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心房細動 (AF) は、世界的に最も蔓延している不整脈の 1 つとして浮上しており、その発生率は継続的に増加しており、それにより公衆衛生上の重大な懸念事項にまで高まっている (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】心房細動 (AF) は、世界的に最も蔓延している不整脈の 1 つとして浮上しており、その発生率は継続的に増加しており、それにより公衆衛生上の重大な懸念事項にまで高まってい… (観察研究・その他 / 症例数: 不明)
 【方法】そして
-【結果】ツリーベースのアンサンブル学習支援リピドミクスを使用して、スフィンゴミエリンが重要な差次的代謝産物として同定され、AF 患者では大幅に減少していることが判明しました。スフィンゴミエリンの外因性補給は、マウスにおける Ach-CaCl2 および Ang II 誘発性の AF、線維症、炎症を大幅に軽減しました。さらに、スフィンゴミエリンレベルの低下は、AF条件下でのスフィンゴミエリンホスホジエステラーゼ（SMPD）の活性の増加に起因すると考えられました。機構的には、RNA-Seq解析により、スフィンゴミエリンがAF誘発性のRap1シグナル伝達経路の活性化を阻害することが実証され、この所見は生体内でのRAP1の過剰発現とノックダウンによって裏付けられた
-【結論】まとめると、これらの発見は、Rap1 シグナル伝達経路の阻害を通じて心房細動を軽減するスフィンゴミエリンおよび SMPD 阻害剤の治療可能性を強調し、それによってスフィンゴミエリン代謝の標的化が実行可能かつ新規な心房細動治療戦略として確立されることになる</t>
+【結果】ツリーベースのアンサンブル学習支援リピドミクスを使用して、スフィンゴミエリンが重要な差次的代謝産物として同定され、AF 患者では大幅に減少していることが判明しました。
+【結論】まとめると、これらの発見は、Rap1 シグナル伝達経路の阻害を通じて心房細動を軽減するスフィンゴミエリンおよび SMPD 阻害剤の治療可能性を強調し、それによってスフィンゴミエリン…</t>
   </si>
   <si>
     <t>Wang L, Shi A, Yu D, Jiang Z, Chen Q, Yu X, et al.. Sphingomyelin as a key negative mediator in atrial fibrillation via lipid proﬁling analysis and functional identiﬁcation.. Europace. 2026 Sep 21;:. doi: 10.1093/europace/euag270 doi.</t>
@@ -1482,9 +1482,9 @@
 (Incorporating a Shortened Long-Term Effectiveness END Point Into Catheter Ablation Trials: Statistical Properties and Implications.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心房細動アブレーションの試験における 6 か月の有効性エンドポイントの使用に関する証拠は限られている。この研究は、発作性心房細動アブレーションの臨床試験の計画に情報を提供することを第二の目的として、アブレーション有効性エンドポイント検出と追跡期間との関係を評価することを目的としている (観察研究・その他 / 症例数: 不明)
-【方法】4 つの前向き研究からの患者レベルのデータが集約された。長期有効性エンドポイントは、(1) 3 か月のブランク期間と 12 か月の追跡調査 (現在)、および (2) 2 か月のブランク期間と 6 か月の追跡調査 (提案) で計算された。感度、特異度、一致度は、現在のエンドポイントと提案されたエンドポイントに基づいて各研究について計算された。線形近似法を使用して 6 か月生存推定値を 12 か月に外挿し、予測された 12 か月生存率を実際の 12 か月生存率と比較しました。線形近似を使用して、新しいパフォーマンス目標が導出され、各研究の 6 か月生存率と比較された
-【結果】現在のエンドポイントと提案されたエンドポイントの比較分析では、最近の 4 つの臨床試験全体で 83% ～ 92% の範囲の一致と 57% ～ 76% の範囲の感度が実証された。線形近似法により、4 つのプールされた研究の推定 12 か月生存率は 72.5% となり、これに対し、真の 12 か月生存率は 71.0% (-1.5% 誤差) であった。各研究の真の 12 か月生存率と個別に比較した場合、推定 12 か月生存率には -3.6% から 0.3% の範囲の誤差が生じました。 6 か月のエンドポイントを使用する試験では、56.2% という新しいパフォーマンス目標が提案されている
+    <t xml:space="preserve">【概要】心房細動アブレーションの試験における 6 か月の有効性エンドポイントの使用に関する証拠は限られている。 (観察研究・その他 / 症例数: 不明)
+【方法】4 つの前向き研究からの患者レベルのデータが集約された。
+【結果】現在のエンドポイントと提案されたエンドポイントの比較分析では、最近の 4 つの臨床試験全体で 83% ～ 92% の範囲の一致と 57% ～ 76% の範囲の感度が実証された。
 【結論】2 か月のブランク期間を含む 6 か月の追跡期間という提案されたエンドポイントは、現在の 12 か月の有効性エンドポイントと妥当なレベルの一致を示しました</t>
   </si>
   <si>
@@ -1504,7 +1504,7 @@
   <si>
     <t xml:space="preserve">【概要】非持続性心室頻拍 (NSVT) は、肥大型心筋症 (HCM) における心臓突然死 (SCD) の危険因子であることが十分に確立されている (観察研究・その他 / 症例数: 不明)
 【方法】そして
-【結果】この後ろ向きの多施設研究には、2625 人の HCM 患者が含まれていました。  24 時間のホルター心電図記録により、NSVT とその特性 (頻度、持続時間、結合間隔) が評価した。  主要エンドポイントはSCDであった。副次評価項目は心血管死と全死因死であった。  2,584 人の患者が分析された (49.6 ± 15.2 歳、62.4% 男性)。  非持続性心室頻拍は 320 人 (12.4%) に発生しました。  中央値4.4年の追跡期間中に、全死因死亡が221人（8.6％）、心血管死が159人（6.2％）、SCDが64人（2.5％）であった。  特性の中で、2 番目のカップリング間隔が有害な結果を最も良く予測しました (最適カットオフ = 394 ミリ秒)。  非持続性心室頻拍の頻度と持続時間は予後を予測しなかった。 単変量解析および多変量解析では、2 番目の結合間隔が 394 ミリ秒未満であると、SCD [ハザード比 (HR) 8.36、95% 信頼区間 (CI) 4.33-16.12、P &lt; 0.001]、心血管死 (HR 3.64、95% CI 2.07-6.37、P &lt; 0.001) のリスクが著しく増加しました。 0.001）、および全死因死亡（HR 3.26、95% CI 1.97-5.41、P &lt; 0.001）とNSVTの非存在との比較では、2回目のカップリング間隔が394ミリ秒以上の場合はそうではなかった。  NSVT を悪性 NSVT (二次結合間隔が短い NSVT) に置き換えることで、SCD リスク アルゴリズムが大幅に改善された
+【結果】この後ろ向きの多施設研究には、2625 人の HCM 患者が含まれていました。
 【結論】NSVT の 2 回目のカップリング間隔が短い場合、長い場合よりも HCM における SCD リスクが高くなりる</t>
   </si>
   <si>
@@ -1586,10 +1586,10 @@
 (First United States Experience With Focal Pulsed-Field Ablation Using the FARAPOINT Catheter for Refractory Ventricular Tachycardia.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】高周波 (RF) アブレーションが失敗した後の薬剤抵抗性の心室頻拍 (VT) は依然として臨床上の課題である。パルスフィールドアブレーション（PFA）は心室用途に拡大していますが、VTにおける焦点パルスフィールド専用カテーテルに関する米国の経験は乏しく、パルスフィールドプラットフォームはメーカー間で同等ではない。ここでは、米国における FARAPOINT 焦点 PFA の最初の経験について説明しる (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】高周波 (RF) アブレーションが失敗した後の薬剤抵抗性の心室頻拍 (VT) は依然として臨床上の課題である。 (観察研究・その他 / 症例数: 不明)
 【方法】そして
-【結果】われわれは、2025年7月から2026年5月までに単一のVAヘルスケアシステムでFARAPOINT（ボストンサイエンティフィック）焦点PFAカテーテルを用いたVTアブレーションを受けた連続10人の患者を遡及的に検討した。全患者は薬剤抵抗性の持続性単形性VTを患っていた。年齢中央値は77歳で、虚血性心筋症と非虚血性心筋症が混在していた。 10 人中 6 人は、以前に少なくとも 1 回カテーテルアブレーションに失敗したことがありました。急性非誘発性は、正式なアブレーション後刺激試験を受けた9人の患者全員で達成された。処置上の合併症は発生しなかった。中央値95.5日の追跡期間中、10人の患者のうち4人で持続性VTが再発した。繰り返しアブレーションを受けた患者も、機械的循環補助を必要とした患者も、死亡した患者もいなかった
-【結論】この米国での最初の経験では、難治性 VT および以前に困難な基質を含むアブレーションに失敗した高リスクコホート内の虚血性心筋症患者に対して、FARAPOINT は安全であり、非常に効果的であった</t>
+【結果】われわれは、2025年7月から2026年5月までに単一のVAヘルスケアシステムでFARAPOINT（ボストンサイエンティフィック）焦点PFAカテーテルを用いたVTアブレーションを受けた連続10人の患者を遡及的に検討した。
+【結論】この米国での最初の経験では、難治性 VT および以前に困難な基質を含むアブレーションに失敗した高リスクコホート内の虚血性心筋症患者に対して、FARAPOINT は安全であり、非常に…</t>
   </si>
   <si>
     <t>Reyes JL, Munshi R, Goebel C, Tholakanahalli V. First United States Experience With Focal Pulsed-Field Ablation Using the FARAPOINT Catheter for Refractory Ventricular Tachycardia.. J Cardiovasc Electrophysiol. 2026 Sep 13;:. doi: 10.1111/jce.70498 doi.</t>
@@ -1628,8 +1628,8 @@
 (Clinical Considerations for the Care of the Tactical Athlete With Cardiovascular Abnormalities: A Scientific Statement From the American College of Cardiology and the American Heart Association.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】米国心臓病学会/米国心臓協会の科学的声明「心血管異常のある戦術アスリートのケアに関する臨床的考慮事項」は、心血管疾患または心血管疾患のリスクのある戦術アスリート (消防士、法執行官、軍隊など) をケアする臨床医、およびこれらのアスリートのケアと健康を監督する組織にガイダンスと教育を提供するために書かれました (観察研究・その他 / 症例数: 不明)
-【方法】この科学的声明は、心血管疾患のプロセスや、戦術的アスリートに特有のタスクを実行する際の潜在的なリスクと利点を考慮する際に関連するその他のトピックに焦点を当てた 11 のセクションで構成されている。  戦術アスリートの分野、スポーツ心臓病学、および対象となるそれぞれのトピックの専門家で構成されるタスクフォースが各セクションに割り当てられ、臨床医が参照するための具体的な「臨床考慮事項表」が作成された。  包括的な文献レビューと、入手可能な場合はアスリートに焦点を当てた戦術データの重視が、提示されたすべての臨床的考察の執筆に不可欠であった。 この枠組みは、最近出版された「心血管異常を持つアスリートのための競技スポーツ参加に関する臨床的考慮事項: 米国心臓協会および米国心臓病学会からの科学的声明」の枠組みを反映している。構造: この文書の特定のセクションには以下が含まれる。 セクション 1: 戦術タスクの分類。セクション 2: 戦術アスリートの参加前の心臓評価。セクション 3: 戦術的臨床管理の倫理的および法的側面。セクション 4: 遺伝性心筋症;セクション 5: 心筋炎およびその他の後天性心臓病;セクション 6: 先天性心疾患;セクション 7: 大動脈疾患、大動脈二尖弁、および自然冠動脈解離。セクション 8: 失神、SCA、不整脈、およびデバイス。セクション9: 心臓ちゃん ネロパチー。セクション 10: 高齢の戦術アスリート。セクション 11: 環境曝露、PED/S、および追加の心臓の状態と考慮事項。 各セクションでは、主要な臨床的考慮事項の理論的根拠と、それぞれの臨床的考慮事項の表を詳しく説明する概要を提供しる
+    <t xml:space="preserve">【概要】米国心臓病学会/米国心臓協会の科学的声明「心血管異常のある戦術アスリートのケアに関する臨床的考慮事項」は、心血管疾患または心血管疾患のリスクのある戦術アスリート (消防士… (観察研究・その他 / 症例数: 不明)
+【方法】この科学的声明は、心血管疾患のプロセスや、戦術的アスリートに特有のタスクを実行する際の潜在的なリスクと利点を考慮する際に関連するその他のトピックに焦点を当てた 11 のセ…
 【結果】戦術アスリートの分野、スポーツ心臓病学、および対象となるそれぞれのトピックの専門家で構成されるタスクフォースが各セクションに割り当てられ、臨床医が参照するための具体的な「臨床考慮事項表」が作成された
 【結論】各セクションでは、主要な臨床的考慮事項の理論的根拠と、それぞれの臨床的考慮事項の表を詳しく説明する概要を提供しる</t>
   </si>
@@ -1700,9 +1700,9 @@
 (Antisense-mediated gene therapy targeting DMPK restores cardiac ion channel function and electrical stability in myotonic dystrophy type 1.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】筋強直性ジストロフィー 1 型 (DM1) は、心臓伝導欠陥や生命を脅かす不整脈を引き起こす有毒な RNA の機能獲得を特徴としている。現在の治療法の選択肢は依然として限られている。目的：DM1患者から作製したヒト人工多能性幹細胞由来心筋細胞（hiPSC-CM）における変異体DMPK転写物を標的とするアンチセンスオリゴヌクレオチド（ASO）であるIONIS-486178の分子的および電気生理学的有効性を評価した (観察研究・その他 / 症例数: 不明)
-【方法】DM1 hiPSC-CM を IONIS-486178 で 24 時間処理しました。有効性は、DMPK ノックダウンおよびスプライシング分析には逆転写定量的ポリメラーゼ連鎖反応、核病巣定量には蛍光 in situ ハイブリダイゼーション、イオンチャネルタンパク質発現にはウェスタンブロット、イオン電流および活動電位特性評価には全細胞パッチクランプを使用してを評価した
-【結果】IONIS-486178 (5 μmol/L) による hiPSC-CM の処理により、DMPK の約 90% ノックダウンが達成され、有毒な核病巣が減少し、成体アイソフォームに向けた SCN5A ミススプライシングが修正された。機能的には、IONIS-486178 は、DM1 hiPSC-CM で減少したすべてのイオン電流 (ナトリウム、L 型カルシウム、カリウム電流) を完全に回復しました。この電気生理学的レスキューは、対応するイオンチャネルタンパク質の再発現と相関していました。この治療により、活動電位の動態と持続時間も正常化され、不整脈誘発性イベントの発生率が大幅に減少しました
+    <t xml:space="preserve">【概要】筋強直性ジストロフィー 1 型 (DM1) は、心臓伝導欠陥や生命を脅かす不整脈を引き起こす有毒な RNA の機能獲得を特徴としている。 (観察研究・その他 / 症例数: 不明)
+【方法】DM1 hiPSC-CM を IONIS-486178 で 24 時間処理しました。
+【結果】IONIS-486178 (5 μmol/L) による hiPSC-CM の処理により、DMPK の約 90% ノックダウンが達成され、有毒な核病巣が減少し、成体アイソフォームに向けた SCN5A ミススプライシングが修…
 【結論】ASO を介した DMPK の抑制は、DM1 のヒト細胞モデルにおいてコア電気生理学的欠陥を逆転させ、不整脈誘発性イベントを軽減するのに十分である</t>
   </si>
   <si>
@@ -1740,9 +1740,9 @@
 (The present and the future of risk stratification for and prevention of sudden cardiac death: A Heart Rhythm Society think tank meeting.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】会議の内容は、(1) SCD の現在の公衆衛生への影響についての理解を深めること、(2) SCD の予測と予防の現状をレビューすること、(3) SCD の予測と予防におけるギャップを特定すること、(4) 特定されたギャップに対処するための行動計画を策定することであった。この原稿は会議の議事を要約し、SCD の負担と影響を軽減するための計画を提案しる (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】会議の内容は、(1) SCD の現在の公衆衛生への影響についての理解を深めること、(2) SCD の予測と予防の現状をレビューすること、(3) SCD の予測と予防におけ… (観察研究・その他 / 症例数: 不明)
 【方法】突然の心停止 (SCA) の治療における多くの進歩にもかかわらず、SCA 患者の 90% は生存できません
-【結果】突然の心停止 (SCA) の治療における多くの進歩にもかかわらず、SCA 患者の 90% は生存できません。 SCD 予防における大きな課題は、SCD の発生率が最も高いのは、以前に持続性心室不整脈を患った患者や心不全患者などの既知の高リスク群であるにもかかわらず、SCD イベントの絶対数が最も多いのは、SCD のリスクが増加していることが現在知られていない個人であることである
+【結果】突然の心停止 (SCA) の治療における多くの進歩にもかかわらず、SCA 患者の 90% は生存できません。
 【結論】この原稿は会議の議事を要約し、SCD の負担と影響を軽減するための計画を提案しる</t>
   </si>
   <si>
@@ -1760,9 +1760,9 @@
 (Progression of persistent atrial fibrillation and impact of ablation: A systematic review and meta-analysis.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】持続性心房細動 (PsAF) は、多くの場合、発作性心房細動と永続性心房細動 (AF) の間の中間段階とみなされる。しかし、その進行経路と管理経路はまだ十分に特徴付けられていません。目的: この研究は、PsAF から永続性 AF への進行率を定量化し、予測因子を特定し、管理経路を説明することを目的としていました (観察研究・その他 / 症例数: 不明)
-【方法】私たちは、2026 年 1 月までに PubMed と Embase で、PsAF から永続性 AF および/または管理経路への進行を報告する研究を系統的に検索しました。 2 人の査読者が独立してデータを抽出し、研究の質を評価しました。ランダム効果メタアナリシスを使用して進行率をプールしました
-【結果】21件の研究のうち; 17 件が一次メタ分析に貢献しました。 PsAF から永続性 AF へのプールされた進行率は、100 人年 (PY) あたり 16.42 であった (95% 信頼区間 11.48 ～ 23.48)。最新の研究（2015年以上）では、以前のコホートよりも低い率が示した（100年間あたり11.06対21.83、P = 0.069）。メタ回帰では、以前の肺静脈隔離の有病率が高いほど、進行は低いと関連していた（10パーセントポイント増加あたり率比0.82、95％信頼区間0.69-0.97、P = 0.027）。年齢、女性の性別、心不全には、研究レベルでの明確な関連性は示されなかった。観察データによれば、可用性が増加しているにもかかわらず、カテーテルアブレーションの利用率は比較的低いことが示されている
+    <t xml:space="preserve">【概要】持続性心房細動 (PsAF) は、多くの場合、発作性心房細動と永続性心房細動 (AF) の間の中間段階とみなされる。 (観察研究・その他 / 症例数: 不明)
+【方法】私たちは、2026 年 1 月までに PubMed と Embase で、PsAF から永続性 AF および/または管理経路への進行を報告する研究を系統的に検索しました。
+【結果】21件の研究のうち; 17 件が一次メタ分析に貢献しました。
 【結論】PsAF の進行は不均一であり、現代のコホートは歴史的なシリーズよりも低い率を示唆している</t>
   </si>
   <si>
@@ -1780,10 +1780,10 @@
 (Cardiac α4β2 nicotinic receptors as a therapeutic target for fatal ventricular arrhythmias.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】および目的: 致死性心室頻脈性不整脈 (FVT) は、世界的に心臓突然死の主な原因となっている。現在の抗不整脈療法は、その臨床的重要性にもかかわらず、有効性が限られており、不整脈誘発のリスクがあるという制約が残っている。内因性心臓コリン作動性シグナル伝達は電気生理学的調節に寄与しているが、この系の重要な構成要素である心室α4β2ニコチン性アセチルコリン受容体（nAChR）を標的としたFVT治療の可能性はまだ解明されていない (観察研究・その他 / 症例数: 不明)
-【方法】薬理学的スクリーニングにより、α4β2 nAChR のポジティブ アロステリック モジュレーター (PAM) が抗不整脈特性を有することが同定された。構造ベースの設計を通じて、サルベージ 1 が開発され、その有効性と安全性プロファイルが、げっ歯類、ブタ、およびヒトの FVT の ex vivo 心臓モデルで評価した。根底にあるメカニズムは、パッチクランプ電気生理学、高解像度光学マッピング、分子動力学シミュレーションを使用して調査された
-【結果】薬理学的スクリーニングにより、α4β2 nAChR の増強が有望な抗不整脈戦略であることが確認した。構造誘導開発により、α4 サブユニット上の Phe312 と Phe316 に選択的に結合して受容体をオープンチャネル状態に安定化する PAM であるサルベージ 1 が得られました。げっ歯類、ブタ、およびヒトの FVT の ex vivo 心臓モデルにおいて、サルベージ 1 は一貫して不整脈の発生を防止し、洞調律を迅速に回復しました。機構的には、サルベージ 1 は、健康な組織の電気生理学を損なうことなく、アセチルコリン依存性電流を増強し、損傷した心筋の伝導速度を選択的に改善し、リエントリーを抑制しました
-【結論】この研究は、心室α4β2 nAChRがFVTの創薬可能な標的であることを特定し、ファーストインクラスの治療候補としてサルベージ1を導入し、それによって心不整脈の薬物療法の新たな方向性を確立した</t>
+    <t xml:space="preserve">【概要】および目的: 致死性心室頻脈性不整脈 (FVT) は、世界的に心臓突然死の主な原因となっている。 (観察研究・その他 / 症例数: 不明)
+【方法】薬理学的スクリーニングにより、α4β2 nAChR のポジティブ アロステリック モジュレーター (PAM) が抗不整脈特性を有することが同定された。
+【結果】薬理学的スクリーニングにより、α4β2 nAChR の増強が有望な抗不整脈戦略であることが確認した。
+【結論】この研究は、心室α4β2 nAChRがFVTの創薬可能な標的であることを特定し、ファーストインクラスの治療候補としてサルベージ1を導入し、それによって心不整脈の薬物療法の新たな方向…</t>
   </si>
   <si>
     <t xml:space="preserve">Eur Heart J
@@ -1801,8 +1801,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】および目的: 修飾遺伝子は異なる臨床表現型を引き起こす可能性がありる (観察研究・その他 / 症例数: 不明)
-【方法】合計1192人のLQTS患者が分析された：638人がLQT1、432人がLQT2、122人がp.Y111C-LQT1変異体のスウェーデン人保因者であった。 MTMR4変異体と臨床重症度との関連性は、重篤な症状（β遮断薬による心停止または失神）を有する患者と無症候性または軽度の症状のある患者をの比較によって評価された。 Tpeak-Tend および T 波の不均一性を含む ECG パラメーターもを評価した
-【結果】LQT1 コホートでは、MTMR4 遺伝子型全体で心臓イベントの有意な減少パターンが見られました (AA:15.9%、Aa:11.6%、aa:6.3%)。一方、LQT2 コホートでは逆の傾向が明らかであった (AA:16.5%、Aa:18.2%、aa:27.6%)。スウェーデン人のコホートでは明らかなパターンは見られなかった。組み合わせた LQT1 コホートでは、軽度/無症候性の 702 人中 15% で aa 遺伝子型が見つかりましたが、重篤な症状のある 58 人中 1.7% で見つかりました (P = 0.002)。逆に、LQT2 では、aa は重症例でより頻繁に発生しました (24.1% 対 11.9%、P = 0.014)。 QTc は MTMR4 と関連していなかったが、再分極マーカーは不整脈リスクの遺伝子特異的な方向性を裏付けていました
+【方法】合計1192人のLQTS患者が分析された：638人がLQT1、432人がLQT2、122人がp.Y111C-LQT1変異体のスウェーデン人保因者であった。
+【結果】LQT1 コホートでは、MTMR4 遺伝子型全体で心臓イベントの有意な減少パターンが見られました (AA:15.9%、Aa:11.6%、aa:6.3%)。
 【結論】ホモ接合症におけるMTMR4マイナー対立遺伝子は、LQTSにおける不整脈リスクに対して遺伝子特異的かつ逆の影響を及ぼしる</t>
   </si>
   <si>
@@ -1821,8 +1821,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】および目的: 心房細動の臨床転帰を比較する大規模なランダム化データ (観察研究・その他 / 症例数: 不明)
-【方法】心房細動患者における直接経口抗凝固薬（DOAC）対ワルファリンの4つの重要なランダム化試験からの患者レベルのデータをプールした、心房細動における非ビタミンKアンタゴニスト経口抗凝固薬の使用をより良く調査するための複数の機関間の協力からのデータが分析された。アジア系人種（アジア人）と非アジア系人種の患者におけるベースラインの特徴と臨床転帰が比較された。人種と治療効果の間の相互作用を評価して、アジア人対非アジア人におけるワルファリンと比較したDOACの相対的な有効性と安全性が調査された。アジア人の体重とクレアチニンクリアランスの範囲にわたる結果も調査された
-【結果】合計10,212人のアジア人の患者と61,471人の非アジア人の患者が特定された。  非アジア人に比べて、アジア人は平均3.2歳若く、体重が20kg軽く、腎機能が悪く（平均クレアチニンクリアランス64.9対77.3mL/分）、脳卒中/一過性脳虚血発作の既往率が高かった（37.2%対26.6%）（それぞれP&lt;.001）。  ワルファリン治療群（治療範囲内の中央値はアジア人で57.7％、非アジア人で66.2％、P &lt; 0.001）では、アジア人は脳卒中／全身性塞栓イベント（SEE）、大出血、頭蓋内出血、胃腸出血、および主要な正味臨床転帰（脳卒中／SEE、大出血、または死亡）の調整後リスクが高かった。 ワルファリンと比較して、標準用量（SD）DOACは、アジア人の脳卒中/SEE（ハザード比[HR] .65、95%信頼区間 .53-.80 vs HR .86、95%信頼区間 .78-.95）、大出血（HR .62 [.52-.75] vs HR .91）のリスクを非アジア人よりも大幅に低下させた。 [.84-.98]）、主要な正味臨床転帰（HR .76 [.68-.85] vs HR .94 [.90-.98]; それぞれ Pint &lt; .02）。  標準用量のDOACは、非アジア人においてのみ胃腸出血を増加させた（アジア人のHR .92 [.69-1.23] vs 非アジア人のHR 1.41 [1.25-1.58]、パイント = 0.009）。  アジア人において、SD DOAC は、幅広い体重およびクレアチニン クリアランスにわたって臨床事象のリスクを軽減しました。 SD DOACと比較して、低用量DOACはアジア人における脳卒中/SEEのリスク（HR 1.57 [1.15-2.13]）および副次的正味臨床転帰（脳卒中/SEE、頭蓋内出血、または死亡; HR 1.23 [1.03-1.48]）を有意に増加させた
+【方法】心房細動患者における直接経口抗凝固薬（DOAC）対ワルファリンの4つの重要なランダム化試験からの患者レベルのデータをプールした、心房細動における非ビタミンKアンタゴニスト…
+【結果】合計10,212人のアジア人の患者と61,471人の非アジア人の患者が特定された。
 【結論】心房細動患者におけるSD DOACとワルファリンの臨床転帰は、一般に、非アジア人種よりもアジア人種の患者でさらに良好であった</t>
   </si>
   <si>
@@ -3259,7 +3259,7 @@
     <t>10.1111/jce.70515 doi</t>
   </si>
   <si>
-    <t>背景: ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。  しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままです。  方法：我々は、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。  急性不完全病変は、体系的な再マッピング後に追加の PFA 適用を必要とする残留伝導として定義されました。  学習フェーズは、セグメント化されたロジスティック回帰と逐次ブロック分析を使用して特定されました。 多変数モデルは、処置期、左心房容積 (LAV)、および後壁の形状を評価しました。  結果: 学習曲線が観察され、最初の 20 回の処置中に不完全な病変形成が最も減少しました。  不完全病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました。  手術段階は不完全病変の主な決定要因であり、初期段階と中期段階ではそれぞれ約 24 倍と 9 倍高いオッズでした。  より大きな LAV は、適度な独立した関連性 (OR 1.009/mL) を示しましたが、後壁の形状は独立した関連性を示しませんでした。 中期の不整脈再発は各期で差はなかったが、後期では追跡期間が短かった。  結論: PVI + PWI を使用したペンタスプライン PFA 中の病変完全性は、処置の経験が増えるにつれて徐々に改善します。  Although larger LAV may contribute modestly to incomplete lesion formation, procedural experience appears to play the predominant role.  体系的な電気解剖学的再マッピングは、かなりの手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要です。</t>
+    <t>背景: ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。  しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままです。  方法：我々は、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。  急性不完全病変は、体系的な再マッピング後に追加の PFA 適用を必要とする残留伝導として定義されました。  学習フェーズは、セグメント化されたロジスティック回帰と逐次ブロック分析を使用して特定されました。 多変数モデルは、処置期、左心房容積 (LAV)、および後壁の形状を評価しました。  結果: 学習曲線が観察され、最初の 20 回の処置中に不完全な病変形成が最も減少しました。  不完全病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました。  手術段階は不完全病変の主な決定要因であり、初期段階と中期段階ではそれぞれ約 24 倍と 9 倍高いオッズでした。  より大きな LAV は、適度な独立した関連性 (OR 1.009/mL) を示しましたが、後壁の形状は独立した関連性を示しませんでした。 中期の不整脈再発は各期で差はなかったが、後期では追跡期間が短かった。  結論: PVI + PWI を使用したペンタスプライン PFA 中の病変完全性は、処置の経験が増えるにつれて徐々に改善します。  LAV が大きいと不完全な病変形成に若干寄与する可能性がありますが、処置の経験が主な役割を果たすと思われます。  体系的な電気解剖学的再マッピングは、かなりの手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3338,7 +3338,7 @@
     <t>10.1007/s10840-026-02443-2 doi</t>
   </si>
   <si>
-    <t>背景: 米国では、パルスフィールドアブレーション(PFA)システムが骨格筋の刺激と不快感を引き起こすため、米国では全身麻酔(GA)が心房細動(AF)カテーテルアブレーションの鎮静戦略として好まれており、より軽い鎮静下では耐えられないことが挙げられます。  最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性があります。  この状況において、MAC がアブレーションの有効性を損なうことなく手技効率の利点を提供するかどうかは、十分に特徴づけられていません。 目的: 年齢に合わせたデザインを使用して、AF に対して BiB PFA (VOLT) を受けている患者において MAC と GA の間で処置のタイミング、アブレーションの有効性、安全性を比較すること。  方法：我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。  各 MAC 患者は、利用可能な最も近い年齢の GA 患者と 1:1 でマッチングされ、39 人の年齢が一致した対照が得られました。  6 つの異なる時間間隔が収集されました: 総室時間、処置前のセットアップ時間、中心処置時間、処置後のターンオーバー時間、経中隔から左心房 (LA) へのシースアウト (滞留) 時間、およびアブレーション カテーテルの滞留時間。 施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較されました。  次に、グループ比較が行われました。  さらに、公開されている EP/手順スイートの 1 分あたりのコスト見積もりを使用して、観察された総室内時間の違いに関連する EP 検査施設のコスト削減とスケジュールの機会コストも決定されました。  結果：総室内時間（103.5 ± 20.0 対 126.2 ± 33.1 分、p = 0.0004）、処置前の準備時間（33.4 ± 10.0 対 50.3 ± 28.0 分、p = 0.0007）、処置後のターンオーバー時間（14.8 ± 9.3 対21.4 ± 8.3 分; p = 0.0030) は MAC の方が有意に短かった。  コア処置時間 (55.3 ± 20.5 対 55.3 ± 23.9 分)、経中隔から LA シースアウトまでの時間 (34.2 ± 12.9 対 55.3 ± 23.9 分) 35.7 ± 18.5 分）はグループ間で有意な差はありませんでした（両方とも p ≥ 0.62）。  アブレーションカテーテルの滞留時間は、MAC の方が若干長くなりました (27.7 ± 11.9 対 24.2 ± 15.5 分; p = 0.036)。  施行された総切除病変数（17.6 ± 5.1 対 18.8 ± 7.2、p = 0.68）および急性処置成功率（39/39 [100%] 対 39/39 [100%]）は、MAC 群と GA 間で同様であり、どちらのグループにも処置上の合併症はありませんでした。  MAC 症例 1 例 (2.6%) は、気道分泌物による咳のため、処置の途中で全身麻酔に変更されました。 公表されている EP/手続きスイートの 1 分あたりのコスト見積もり (29 ドルから 60 ドル/分) を、観測された合計在室時間の 22.7 分の削減に適用すると、MAC は 1 件あたりの設備コストの推定 658 ドルから 1,362 ドルの節約に関連しており、追加のケースのスケジュール設定による潜在的な機会費用の利点が見られました。  CONCLUSION: In an age-matched cohort undergoing BiB PFA (VOLT) for AF, MAC was associated with shorter total room time, pre-procedure setup time, and post-procedure turnover time than GA, with no difference in ablation lesion delivery, acute success, or complications. MAC による麻酔関連の時間の節約は、アブレーション処置自体ではなく、部屋のロジスティクスに集中しているようで、この小規模コホートでは急性処置の結果に検出可能な差はなく、MAC が BiB PFA に対する GA に代わる合理的な代替品として支持されています。</t>
+    <t>背景: 米国では、パルスフィールドアブレーション(PFA)システムが骨格筋の刺激と不快感を引き起こすため、米国では全身麻酔(GA)が心房細動(AF)カテーテルアブレーションの鎮静戦略として好まれており、より軽い鎮静下では耐えられないことが挙げられます。  最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性があります。  この状況において、MAC がアブレーションの有効性を損なうことなく手技効率の利点を提供するかどうかは、十分に特徴づけられていません。 目的: 年齢に合わせたデザインを使用して、AF に対して BiB PFA (VOLT) を受けている患者において MAC と GA の間で処置のタイミング、アブレーションの有効性、安全性を比較すること。  方法：我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。  各 MAC 患者は、利用可能な最も近い年齢の GA 患者と 1:1 でマッチングされ、39 人の年齢が一致した対照が得られました。  6 つの異なる時間間隔が収集されました: 総室時間、処置前のセットアップ時間、中心処置時間、処置後のターンオーバー時間、経中隔から左心房 (LA) へのシースアウト (滞留) 時間、およびアブレーション カテーテルの滞留時間。 施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較されました。  次に、グループ比較が行われました。  さらに、公開されている EP/手順スイートの 1 分あたりのコスト見積もりを使用して、観察された総室内時間の違いに関連する EP 検査施設のコスト削減とスケジュールの機会コストも決定されました。  結果：総室内時間（103.5 ± 20.0 対 126.2 ± 33.1 分、p = 0.0004）、処置前の準備時間（33.4 ± 10.0 対 50.3 ± 28.0 分、p = 0.0007）、処置後のターンオーバー時間（14.8 ± 9.3 対21.4 ± 8.3 分; p = 0.0030) は MAC の方が有意に短かった。  コア処置時間 (55.3 ± 20.5 対 55.3 ± 23.9 分)、経中隔から LA シースアウトまでの時間 (34.2 ± 12.9 対 55.3 ± 23.9 分) 35.7 ± 18.5 分）はグループ間で有意な差はありませんでした（両方とも p ≥ 0.62）。  アブレーションカテーテルの滞留時間は、MAC の方が若干長くなりました (27.7 ± 11.9 対 24.2 ± 15.5 分; p = 0.036)。  施行された総切除病変数（17.6 ± 5.1 対 18.8 ± 7.2、p = 0.68）および急性処置成功率（39/39 [100%] 対 39/39 [100%]）は、MAC 群と GA 間で同様であり、どちらのグループにも処置上の合併症はありませんでした。  MAC 症例 1 例 (2.6%) は、気道分泌物による咳のため、処置の途中で全身麻酔に変更されました。 公表されている EP/手続きスイートの 1 分あたりのコスト見積もり (29 ドルから 60 ドル/分) を、観測された合計在室時間の 22.7 分の削減に適用すると、MAC は 1 件あたりの設備コストの推定 658 ドルから 1,362 ドルの節約に関連しており、追加のケースのスケジュール設定による潜在的な機会費用の利点が見られました。  結論： AF に対して BiB PFA (VOLT) を受けた年齢を一致させたコホートでは、MAC は GA よりも総室時間、処置前のセットアップ時間、および処置後のターンオーバー時間の短縮と関連しており、アブレーション病変の送達、急性成功、または合併症には差がありませんでした。 MAC による麻酔関連の時間の節約は、アブレーション処置自体ではなく、部屋のロジスティクスに集中しているようで、この小規模コホートでは急性処置の結果に検出可能な差はなく、MAC が BiB PFA に対する GA に代わる合理的な代替品として支持されています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -4876,7 +4876,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>2</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>3</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" ht="212" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>4</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" ht="116" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>6</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -5058,7 +5058,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>8</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>9</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>10</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>11</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>12</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>13</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>14</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>15</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="20" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>16</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>17</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>18</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>19</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>20</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="25" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>21</v>
       </c>
@@ -5422,7 +5422,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" ht="212" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>22</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>23</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="28" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>24</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="29" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>25</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="30" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>26</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="31" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>27</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="32" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>28</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>29</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="34" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>30</v>
       </c>
@@ -5656,7 +5656,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="35" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>31</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="36" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
         <v>32</v>
       </c>
@@ -5708,7 +5708,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="37" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>33</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="38" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
         <v>34</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="39" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>35</v>
       </c>
@@ -5786,7 +5786,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="40" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
         <v>36</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="41" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>37</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="42" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
         <v>38</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="43" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>39</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="47" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>43</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="48" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>44</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="49" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>45</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="51" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>47</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="52" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>48</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="55" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>51</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="57" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>53</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="58" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="11">
         <v>54</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="61" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>57</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="62" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>58</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="65" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>61</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="66" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>62</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="71" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>67</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="73" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>69</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="77" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>73</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="79" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>75</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="80" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
         <v>76</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="81" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>77</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="82" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="11">
         <v>78</v>
       </c>
@@ -6904,7 +6904,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="83" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>79</v>
       </c>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="B16" s="25"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>802</v>
       </c>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="B16" s="25"/>
     </row>
-    <row r="17" ht="861" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="804" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>822</v>
       </c>
